--- a/research/traditional_assets/database/data/malaysia/malaysia_entertainment.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_entertainment.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1061455245550004</v>
+        <v>0.1059249752960684</v>
       </c>
       <c r="C2">
-        <v>34.87389834929333</v>
+        <v>34.61634557985821</v>
       </c>
       <c r="D2">
-        <v>29.31389834929334</v>
+        <v>29.40582557985821</v>
       </c>
       <c r="E2">
-        <v>-0.848</v>
+        <v>-0.49852</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.34948</v>
       </c>
       <c r="G2">
         <v>5.56</v>
@@ -1439,28 +1439,28 @@
         <v>2.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.017578844</v>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>2.582421156</v>
       </c>
       <c r="O2">
-        <v>0.624</v>
+        <v>0.61978107744</v>
       </c>
       <c r="P2">
-        <v>1.976</v>
+        <v>1.96264007856</v>
       </c>
       <c r="Q2">
-        <v>2.316</v>
+        <v>2.30264007856</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1061455245550004</v>
+        <v>0.1066087831273418</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.025323442738834</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>147.9050613339535</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1059249752960684</v>
+        <v>0.1057044260371364</v>
       </c>
       <c r="C3">
-        <v>34.61634557985821</v>
+        <v>34.35937118452968</v>
       </c>
       <c r="D3">
-        <v>29.40582557985821</v>
+        <v>29.49833118452968</v>
       </c>
       <c r="E3">
-        <v>-0.49852</v>
+        <v>-0.14904</v>
       </c>
       <c r="F3">
-        <v>0.34948</v>
+        <v>0.69896</v>
       </c>
       <c r="G3">
         <v>5.56</v>
@@ -1521,28 +1521,28 @@
         <v>2.6</v>
       </c>
       <c r="M3">
-        <v>0.017578844</v>
+        <v>0.035157688</v>
       </c>
       <c r="N3">
-        <v>2.582421156</v>
+        <v>2.564842312</v>
       </c>
       <c r="O3">
-        <v>0.61978107744</v>
+        <v>0.61556215488</v>
       </c>
       <c r="P3">
-        <v>1.96264007856</v>
+        <v>1.94928015712</v>
       </c>
       <c r="Q3">
-        <v>2.30264007856</v>
+        <v>2.28928015712</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1066087831273418</v>
+        <v>0.1070814959562617</v>
       </c>
       <c r="T3">
-        <v>1.025323442738834</v>
+        <v>1.033294060143887</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>147.9050613339535</v>
+        <v>73.95253066697674</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1057044260371364</v>
+        <v>0.1054838767782044</v>
       </c>
       <c r="C4">
-        <v>34.35937118452968</v>
+        <v>34.10298063892564</v>
       </c>
       <c r="D4">
-        <v>29.49833118452968</v>
+        <v>29.59142063892564</v>
       </c>
       <c r="E4">
-        <v>-0.14904</v>
+        <v>0.2004400000000001</v>
       </c>
       <c r="F4">
-        <v>0.69896</v>
+        <v>1.04844</v>
       </c>
       <c r="G4">
         <v>5.56</v>
@@ -1603,28 +1603,28 @@
         <v>2.6</v>
       </c>
       <c r="M4">
-        <v>0.035157688</v>
+        <v>0.052736532</v>
       </c>
       <c r="N4">
-        <v>2.564842312</v>
+        <v>2.547263468</v>
       </c>
       <c r="O4">
-        <v>0.61556215488</v>
+        <v>0.61134323232</v>
       </c>
       <c r="P4">
-        <v>1.94928015712</v>
+        <v>1.93592023568</v>
       </c>
       <c r="Q4">
-        <v>2.28928015712</v>
+        <v>2.27592023568</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1070814959562617</v>
+        <v>0.1075639554414478</v>
       </c>
       <c r="T4">
-        <v>1.033294060143887</v>
+        <v>1.041429020175848</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.95253066697674</v>
+        <v>49.30168711131783</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1054838767782044</v>
+        <v>0.1052633275192724</v>
       </c>
       <c r="C5">
-        <v>34.10298063892564</v>
+        <v>33.84717948800158</v>
       </c>
       <c r="D5">
-        <v>29.59142063892564</v>
+        <v>29.68509948800158</v>
       </c>
       <c r="E5">
-        <v>0.2004400000000001</v>
+        <v>0.5499200000000001</v>
       </c>
       <c r="F5">
-        <v>1.04844</v>
+        <v>1.39792</v>
       </c>
       <c r="G5">
         <v>5.56</v>
@@ -1685,28 +1685,28 @@
         <v>2.6</v>
       </c>
       <c r="M5">
-        <v>0.052736532</v>
+        <v>0.070315376</v>
       </c>
       <c r="N5">
-        <v>2.547263468</v>
+        <v>2.529684624</v>
       </c>
       <c r="O5">
-        <v>0.61134323232</v>
+        <v>0.60712430976</v>
       </c>
       <c r="P5">
-        <v>1.93592023568</v>
+        <v>1.92256031424</v>
       </c>
       <c r="Q5">
-        <v>2.27592023568</v>
+        <v>2.26256031424</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1075639554414478</v>
+        <v>0.1080564661659088</v>
       </c>
       <c r="T5">
-        <v>1.041429020175848</v>
+        <v>1.049733458541809</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.30168711131783</v>
+        <v>36.97626533348837</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1052633275192724</v>
+        <v>0.1050427782603404</v>
       </c>
       <c r="C6">
-        <v>33.84717948800158</v>
+        <v>33.59197334715164</v>
       </c>
       <c r="D6">
-        <v>29.68509948800158</v>
+        <v>29.77937334715164</v>
       </c>
       <c r="E6">
-        <v>0.5499200000000001</v>
+        <v>0.8994000000000001</v>
       </c>
       <c r="F6">
-        <v>1.39792</v>
+        <v>1.7474</v>
       </c>
       <c r="G6">
         <v>5.56</v>
@@ -1767,28 +1767,28 @@
         <v>2.6</v>
       </c>
       <c r="M6">
-        <v>0.070315376</v>
+        <v>0.08789422</v>
       </c>
       <c r="N6">
-        <v>2.529684624</v>
+        <v>2.51210578</v>
       </c>
       <c r="O6">
-        <v>0.60712430976</v>
+        <v>0.6029053872</v>
       </c>
       <c r="P6">
-        <v>1.92256031424</v>
+        <v>1.9092003928</v>
       </c>
       <c r="Q6">
-        <v>2.26256031424</v>
+        <v>2.2492003928</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1080564661659088</v>
+        <v>0.1085593455372004</v>
       </c>
       <c r="T6">
-        <v>1.049733458541809</v>
+        <v>1.058212727189158</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.97626533348837</v>
+        <v>29.5810122667907</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1050427782603404</v>
+        <v>0.1048222290014084</v>
       </c>
       <c r="C7">
-        <v>33.59197334715164</v>
+        <v>33.33736790333058</v>
       </c>
       <c r="D7">
-        <v>29.77937334715164</v>
+        <v>29.87424790333058</v>
       </c>
       <c r="E7">
-        <v>0.8994000000000001</v>
+        <v>1.24888</v>
       </c>
       <c r="F7">
-        <v>1.7474</v>
+        <v>2.09688</v>
       </c>
       <c r="G7">
         <v>5.56</v>
@@ -1849,28 +1849,28 @@
         <v>2.6</v>
       </c>
       <c r="M7">
-        <v>0.08789422</v>
+        <v>0.105473064</v>
       </c>
       <c r="N7">
-        <v>2.51210578</v>
+        <v>2.494526936</v>
       </c>
       <c r="O7">
-        <v>0.6029053872</v>
+        <v>0.59868646464</v>
       </c>
       <c r="P7">
-        <v>1.9092003928</v>
+        <v>1.89584047136</v>
       </c>
       <c r="Q7">
-        <v>2.2492003928</v>
+        <v>2.23584047136</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1085593455372004</v>
+        <v>0.1090729244695834</v>
       </c>
       <c r="T7">
-        <v>1.058212727189158</v>
+        <v>1.066872405807727</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.5810122667907</v>
+        <v>24.65084355565891</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1048222290014084</v>
+        <v>0.1046016797424764</v>
       </c>
       <c r="C8">
-        <v>33.33736790333058</v>
+        <v>33.08336891619749</v>
       </c>
       <c r="D8">
-        <v>29.87424790333058</v>
+        <v>29.96972891619749</v>
       </c>
       <c r="E8">
-        <v>1.24888</v>
+        <v>1.59836</v>
       </c>
       <c r="F8">
-        <v>2.09688</v>
+        <v>2.44636</v>
       </c>
       <c r="G8">
         <v>5.56</v>
@@ -1931,28 +1931,28 @@
         <v>2.6</v>
       </c>
       <c r="M8">
-        <v>0.105473064</v>
+        <v>0.123051908</v>
       </c>
       <c r="N8">
-        <v>2.494526936</v>
+        <v>2.476948092</v>
       </c>
       <c r="O8">
-        <v>0.59868646464</v>
+        <v>0.5944675420800001</v>
       </c>
       <c r="P8">
-        <v>1.89584047136</v>
+        <v>1.88248054992</v>
       </c>
       <c r="Q8">
-        <v>2.23584047136</v>
+        <v>2.22248054992</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1090729244695834</v>
+        <v>0.1095975481101897</v>
       </c>
       <c r="T8">
-        <v>1.066872405807727</v>
+        <v>1.075718314074007</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.65084355565891</v>
+        <v>21.12929447627907</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1046016797424764</v>
+        <v>0.1043811304835444</v>
       </c>
       <c r="C9">
-        <v>33.08336891619749</v>
+        <v>32.82998221928123</v>
       </c>
       <c r="D9">
-        <v>29.96972891619749</v>
+        <v>30.06582221928122</v>
       </c>
       <c r="E9">
-        <v>1.59836</v>
+        <v>1.94784</v>
       </c>
       <c r="F9">
-        <v>2.44636</v>
+        <v>2.79584</v>
       </c>
       <c r="G9">
         <v>5.56</v>
@@ -2013,28 +2013,28 @@
         <v>2.6</v>
       </c>
       <c r="M9">
-        <v>0.123051908</v>
+        <v>0.140630752</v>
       </c>
       <c r="N9">
-        <v>2.476948092</v>
+        <v>2.459369248</v>
       </c>
       <c r="O9">
-        <v>0.5944675420800001</v>
+        <v>0.5902486195200001</v>
       </c>
       <c r="P9">
-        <v>1.88248054992</v>
+        <v>1.86912062848</v>
       </c>
       <c r="Q9">
-        <v>2.22248054992</v>
+        <v>2.20912062848</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1095975481101897</v>
+        <v>0.1101335766125483</v>
       </c>
       <c r="T9">
-        <v>1.075718314074007</v>
+        <v>1.084756524693903</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.12929447627907</v>
+        <v>18.48813266674419</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1043811304835444</v>
+        <v>0.1041605812246124</v>
       </c>
       <c r="C10">
-        <v>32.82998221928123</v>
+        <v>32.57721372116855</v>
       </c>
       <c r="D10">
-        <v>30.06582221928122</v>
+        <v>30.16253372116855</v>
       </c>
       <c r="E10">
-        <v>1.94784</v>
+        <v>2.29732</v>
       </c>
       <c r="F10">
-        <v>2.79584</v>
+        <v>3.14532</v>
       </c>
       <c r="G10">
         <v>5.56</v>
@@ -2095,28 +2095,28 @@
         <v>2.6</v>
       </c>
       <c r="M10">
-        <v>0.140630752</v>
+        <v>0.158209596</v>
       </c>
       <c r="N10">
-        <v>2.459369248</v>
+        <v>2.441790404</v>
       </c>
       <c r="O10">
-        <v>0.5902486195200001</v>
+        <v>0.5860296969600001</v>
       </c>
       <c r="P10">
-        <v>1.86912062848</v>
+        <v>1.85576070704</v>
       </c>
       <c r="Q10">
-        <v>2.20912062848</v>
+        <v>2.19576070704</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1101335766125483</v>
+        <v>0.1106813859611125</v>
       </c>
       <c r="T10">
-        <v>1.084756524693903</v>
+        <v>1.093993377305444</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.48813266674419</v>
+        <v>16.43389570377261</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1041605812246124</v>
+        <v>0.1039400319656804</v>
       </c>
       <c r="C11">
-        <v>32.57721372116855</v>
+        <v>32.32506940671522</v>
       </c>
       <c r="D11">
-        <v>30.16253372116855</v>
+        <v>30.25986940671522</v>
       </c>
       <c r="E11">
-        <v>2.29732</v>
+        <v>2.6468</v>
       </c>
       <c r="F11">
-        <v>3.14532</v>
+        <v>3.4948</v>
       </c>
       <c r="G11">
         <v>5.56</v>
@@ -2177,28 +2177,28 @@
         <v>2.6</v>
       </c>
       <c r="M11">
-        <v>0.158209596</v>
+        <v>0.17578844</v>
       </c>
       <c r="N11">
-        <v>2.441790404</v>
+        <v>2.42421156</v>
       </c>
       <c r="O11">
-        <v>0.5860296969600001</v>
+        <v>0.5818107744000001</v>
       </c>
       <c r="P11">
-        <v>1.85576070704</v>
+        <v>1.8424007856</v>
       </c>
       <c r="Q11">
-        <v>2.19576070704</v>
+        <v>2.1824007856</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1106813859611125</v>
+        <v>0.111241368850756</v>
       </c>
       <c r="T11">
-        <v>1.093993377305444</v>
+        <v>1.103435493308353</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.43389570377261</v>
+        <v>14.79050613339535</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1039400319656804</v>
+        <v>0.1037194827067484</v>
       </c>
       <c r="C12">
-        <v>32.32506940671522</v>
+        <v>32.07355533828053</v>
       </c>
       <c r="D12">
-        <v>30.25986940671522</v>
+        <v>30.35783533828053</v>
       </c>
       <c r="E12">
-        <v>2.6468</v>
+        <v>2.99628</v>
       </c>
       <c r="F12">
-        <v>3.4948</v>
+        <v>3.84428</v>
       </c>
       <c r="G12">
         <v>5.56</v>
@@ -2259,28 +2259,28 @@
         <v>2.6</v>
       </c>
       <c r="M12">
-        <v>0.17578844</v>
+        <v>0.193367284</v>
       </c>
       <c r="N12">
-        <v>2.42421156</v>
+        <v>2.406632716</v>
       </c>
       <c r="O12">
-        <v>0.5818107744000001</v>
+        <v>0.5775918518400001</v>
       </c>
       <c r="P12">
-        <v>1.8424007856</v>
+        <v>1.82904086416</v>
       </c>
       <c r="Q12">
-        <v>2.1824007856</v>
+        <v>2.16904086416</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.111241368850756</v>
+        <v>0.11181393562556</v>
       </c>
       <c r="T12">
-        <v>1.103435493308353</v>
+        <v>1.113089791693349</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.79050613339535</v>
+        <v>13.44591466672305</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1037194827067484</v>
+        <v>0.1036357334478164</v>
       </c>
       <c r="C13">
-        <v>32.07355533828053</v>
+        <v>31.76144235550163</v>
       </c>
       <c r="D13">
-        <v>30.35783533828053</v>
+        <v>30.39520235550163</v>
       </c>
       <c r="E13">
-        <v>2.99628</v>
+        <v>3.34576</v>
       </c>
       <c r="F13">
-        <v>3.84428</v>
+        <v>4.19376</v>
       </c>
       <c r="G13">
         <v>5.56</v>
@@ -2341,45 +2341,45 @@
         <v>2.6</v>
       </c>
       <c r="M13">
-        <v>0.193367284</v>
+        <v>0.217236768</v>
       </c>
       <c r="N13">
-        <v>2.406632716</v>
+        <v>2.382763232</v>
       </c>
       <c r="O13">
-        <v>0.5775918518400001</v>
+        <v>0.57186317568</v>
       </c>
       <c r="P13">
-        <v>1.82904086416</v>
+        <v>1.81090005632</v>
       </c>
       <c r="Q13">
-        <v>2.16904086416</v>
+        <v>2.15090005632</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.11181393562556</v>
+        <v>0.1123995152816095</v>
       </c>
       <c r="T13">
-        <v>1.113089791693349</v>
+        <v>1.122963505950732</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.44591466672305</v>
+        <v>11.9685080197842</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1036357334478164</v>
+        <v>0.1034265841888844</v>
       </c>
       <c r="C14">
-        <v>31.76144235550163</v>
+        <v>31.50568295788879</v>
       </c>
       <c r="D14">
-        <v>30.39520235550163</v>
+        <v>30.48892295788879</v>
       </c>
       <c r="E14">
-        <v>3.34576</v>
+        <v>3.69524</v>
       </c>
       <c r="F14">
-        <v>4.19376</v>
+        <v>4.54324</v>
       </c>
       <c r="G14">
         <v>5.56</v>
@@ -2423,28 +2423,28 @@
         <v>2.6</v>
       </c>
       <c r="M14">
-        <v>0.217236768</v>
+        <v>0.235339832</v>
       </c>
       <c r="N14">
-        <v>2.382763232</v>
+        <v>2.364660168</v>
       </c>
       <c r="O14">
-        <v>0.57186317568</v>
+        <v>0.56751844032</v>
       </c>
       <c r="P14">
-        <v>1.81090005632</v>
+        <v>1.79714172768</v>
       </c>
       <c r="Q14">
-        <v>2.15090005632</v>
+        <v>2.13714172768</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1123995152816095</v>
+        <v>0.1129985565389476</v>
       </c>
       <c r="T14">
-        <v>1.122963505950732</v>
+        <v>1.133064202145067</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.9685080197842</v>
+        <v>11.04785355672388</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1034265841888844</v>
+        <v>0.1032174349299524</v>
       </c>
       <c r="C15">
-        <v>31.50568295788879</v>
+        <v>31.2505033042887</v>
       </c>
       <c r="D15">
-        <v>30.48892295788879</v>
+        <v>30.58322330428869</v>
       </c>
       <c r="E15">
-        <v>3.69524</v>
+        <v>4.044720000000001</v>
       </c>
       <c r="F15">
-        <v>4.54324</v>
+        <v>4.892720000000001</v>
       </c>
       <c r="G15">
         <v>5.56</v>
@@ -2505,28 +2505,28 @@
         <v>2.6</v>
       </c>
       <c r="M15">
-        <v>0.235339832</v>
+        <v>0.253442896</v>
       </c>
       <c r="N15">
-        <v>2.364660168</v>
+        <v>2.346557104</v>
       </c>
       <c r="O15">
-        <v>0.56751844032</v>
+        <v>0.56317370496</v>
       </c>
       <c r="P15">
-        <v>1.79714172768</v>
+        <v>1.78338339904</v>
       </c>
       <c r="Q15">
-        <v>2.13714172768</v>
+        <v>2.12338339904</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1129985565389476</v>
+        <v>0.1136115289883168</v>
       </c>
       <c r="T15">
-        <v>1.133064202145067</v>
+        <v>1.143399798250897</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.04785355672388</v>
+        <v>10.25872115981503</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1032174349299524</v>
+        <v>0.1032020856710204</v>
       </c>
       <c r="C16">
-        <v>31.2505033042887</v>
+        <v>30.90796689532636</v>
       </c>
       <c r="D16">
-        <v>30.58322330428869</v>
+        <v>30.59016689532636</v>
       </c>
       <c r="E16">
-        <v>4.044720000000001</v>
+        <v>4.394200000000001</v>
       </c>
       <c r="F16">
-        <v>4.892720000000001</v>
+        <v>5.2422</v>
       </c>
       <c r="G16">
         <v>5.56</v>
@@ -2587,45 +2587,45 @@
         <v>2.6</v>
       </c>
       <c r="M16">
-        <v>0.253442896</v>
+        <v>0.2804577</v>
       </c>
       <c r="N16">
-        <v>2.346557104</v>
+        <v>2.3195423</v>
       </c>
       <c r="O16">
-        <v>0.56317370496</v>
+        <v>0.556690152</v>
       </c>
       <c r="P16">
-        <v>1.78338339904</v>
+        <v>1.762852148</v>
       </c>
       <c r="Q16">
-        <v>2.12338339904</v>
+        <v>2.102852148</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1136115289883168</v>
+        <v>0.1142389243188476</v>
       </c>
       <c r="T16">
-        <v>1.143399798250897</v>
+        <v>1.153978584853335</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.25872115981503</v>
+        <v>9.270560230651538</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1032020856710204</v>
+        <v>0.1030058564120884</v>
       </c>
       <c r="C17">
-        <v>30.90796689532637</v>
+        <v>30.64753434035979</v>
       </c>
       <c r="D17">
-        <v>30.59016689532637</v>
+        <v>30.67921434035978</v>
       </c>
       <c r="E17">
-        <v>4.3942</v>
+        <v>4.74368</v>
       </c>
       <c r="F17">
-        <v>5.2422</v>
+        <v>5.59168</v>
       </c>
       <c r="G17">
         <v>5.56</v>
@@ -2669,28 +2669,28 @@
         <v>2.6</v>
       </c>
       <c r="M17">
-        <v>0.2804577</v>
+        <v>0.29915488</v>
       </c>
       <c r="N17">
-        <v>2.3195423</v>
+        <v>2.30084512</v>
       </c>
       <c r="O17">
-        <v>0.556690152</v>
+        <v>0.5522028287999999</v>
       </c>
       <c r="P17">
-        <v>1.762852148</v>
+        <v>1.7486422912</v>
       </c>
       <c r="Q17">
-        <v>2.102852148</v>
+        <v>2.0886422912</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1142389243188475</v>
+        <v>0.1148812576334386</v>
       </c>
       <c r="T17">
-        <v>1.153978584853335</v>
+        <v>1.16480924732726</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.27056023065154</v>
+        <v>8.691150216235817</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1030058564120884</v>
+        <v>0.1028096271531564</v>
       </c>
       <c r="C18">
-        <v>30.64753434035979</v>
+        <v>30.38762173007784</v>
       </c>
       <c r="D18">
-        <v>30.67921434035978</v>
+        <v>30.76878173007784</v>
       </c>
       <c r="E18">
-        <v>4.74368</v>
+        <v>5.093160000000001</v>
       </c>
       <c r="F18">
-        <v>5.59168</v>
+        <v>5.941160000000001</v>
       </c>
       <c r="G18">
         <v>5.56</v>
@@ -2751,28 +2751,28 @@
         <v>2.6</v>
       </c>
       <c r="M18">
-        <v>0.29915488</v>
+        <v>0.31785206</v>
       </c>
       <c r="N18">
-        <v>2.30084512</v>
+        <v>2.28214794</v>
       </c>
       <c r="O18">
-        <v>0.5522028287999999</v>
+        <v>0.5477155056</v>
       </c>
       <c r="P18">
-        <v>1.7486422912</v>
+        <v>1.7344324344</v>
       </c>
       <c r="Q18">
-        <v>2.0886422912</v>
+        <v>2.0744324344</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1148812576334386</v>
+        <v>0.1155390688592246</v>
       </c>
       <c r="T18">
-        <v>1.16480924732726</v>
+        <v>1.175900889619834</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.691150216235817</v>
+        <v>8.179906085869003</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1028096271531564</v>
+        <v>0.1026133978942244</v>
       </c>
       <c r="C19">
-        <v>30.38762173007784</v>
+        <v>30.12823363172073</v>
       </c>
       <c r="D19">
-        <v>30.76878173007784</v>
+        <v>30.85887363172073</v>
       </c>
       <c r="E19">
-        <v>5.093160000000001</v>
+        <v>5.442640000000001</v>
       </c>
       <c r="F19">
-        <v>5.941160000000001</v>
+        <v>6.290640000000001</v>
       </c>
       <c r="G19">
         <v>5.56</v>
@@ -2833,28 +2833,28 @@
         <v>2.6</v>
       </c>
       <c r="M19">
-        <v>0.31785206</v>
+        <v>0.33654924</v>
       </c>
       <c r="N19">
-        <v>2.28214794</v>
+        <v>2.26345076</v>
       </c>
       <c r="O19">
-        <v>0.5477155056</v>
+        <v>0.5432281823999999</v>
       </c>
       <c r="P19">
-        <v>1.7344324344</v>
+        <v>1.7202225776</v>
       </c>
       <c r="Q19">
-        <v>2.0744324344</v>
+        <v>2.0602225776</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1155390688592246</v>
+        <v>0.1162129242612493</v>
       </c>
       <c r="T19">
-        <v>1.175900889619834</v>
+        <v>1.187263059773202</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.179906085869003</v>
+        <v>7.725466858876281</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1026133978942244</v>
+        <v>0.1025326886352924</v>
       </c>
       <c r="C20">
-        <v>30.12823363172072</v>
+        <v>29.81596181411727</v>
       </c>
       <c r="D20">
-        <v>30.85887363172072</v>
+        <v>30.89608181411727</v>
       </c>
       <c r="E20">
-        <v>5.44264</v>
+        <v>5.792120000000001</v>
       </c>
       <c r="F20">
-        <v>6.29064</v>
+        <v>6.64012</v>
       </c>
       <c r="G20">
         <v>5.56</v>
@@ -2915,45 +2915,45 @@
         <v>2.6</v>
       </c>
       <c r="M20">
-        <v>0.33654924</v>
+        <v>0.3605585160000001</v>
       </c>
       <c r="N20">
-        <v>2.26345076</v>
+        <v>2.239441484</v>
       </c>
       <c r="O20">
-        <v>0.5432281823999999</v>
+        <v>0.5374659561599999</v>
       </c>
       <c r="P20">
-        <v>1.7202225776</v>
+        <v>1.70197552784</v>
       </c>
       <c r="Q20">
-        <v>2.0602225776</v>
+        <v>2.04197552784</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1162129242612493</v>
+        <v>0.1169034180682622</v>
       </c>
       <c r="T20">
-        <v>1.187263059773201</v>
+        <v>1.198905777337764</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.725466858876283</v>
+        <v>7.211034782492836</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1025326886352924</v>
+        <v>0.1023425393763604</v>
       </c>
       <c r="C21">
-        <v>29.81596181411727</v>
+        <v>29.55449921453902</v>
       </c>
       <c r="D21">
-        <v>30.89608181411727</v>
+        <v>30.98409921453902</v>
       </c>
       <c r="E21">
-        <v>5.792120000000001</v>
+        <v>6.1416</v>
       </c>
       <c r="F21">
-        <v>6.64012</v>
+        <v>6.9896</v>
       </c>
       <c r="G21">
         <v>5.56</v>
@@ -2997,28 +2997,28 @@
         <v>2.6</v>
       </c>
       <c r="M21">
-        <v>0.3605585160000001</v>
+        <v>0.37953528</v>
       </c>
       <c r="N21">
-        <v>2.239441484</v>
+        <v>2.22046472</v>
       </c>
       <c r="O21">
-        <v>0.5374659561599999</v>
+        <v>0.5329115327999999</v>
       </c>
       <c r="P21">
-        <v>1.70197552784</v>
+        <v>1.6875531872</v>
       </c>
       <c r="Q21">
-        <v>2.04197552784</v>
+        <v>2.0275531872</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1169034180682622</v>
+        <v>0.1176111742204505</v>
       </c>
       <c r="T21">
-        <v>1.198905777337764</v>
+        <v>1.21083956284144</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.211034782492836</v>
+        <v>6.850483043368194</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1023425393763604</v>
+        <v>0.1021523901174284</v>
       </c>
       <c r="C22">
-        <v>29.55449921453902</v>
+        <v>29.29353953930374</v>
       </c>
       <c r="D22">
-        <v>30.98409921453902</v>
+        <v>31.07261953930374</v>
       </c>
       <c r="E22">
-        <v>6.1416</v>
+        <v>6.491080000000001</v>
       </c>
       <c r="F22">
-        <v>6.9896</v>
+        <v>7.339080000000001</v>
       </c>
       <c r="G22">
         <v>5.56</v>
@@ -3079,28 +3079,28 @@
         <v>2.6</v>
       </c>
       <c r="M22">
-        <v>0.37953528</v>
+        <v>0.3985120440000001</v>
       </c>
       <c r="N22">
-        <v>2.22046472</v>
+        <v>2.201487956</v>
       </c>
       <c r="O22">
-        <v>0.5329115327999999</v>
+        <v>0.52835710944</v>
       </c>
       <c r="P22">
-        <v>1.6875531872</v>
+        <v>1.67313084656</v>
       </c>
       <c r="Q22">
-        <v>2.0275531872</v>
+        <v>2.01313084656</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1176111742204505</v>
+        <v>0.1183368482499094</v>
       </c>
       <c r="T22">
-        <v>1.21083956284144</v>
+        <v>1.223075469497108</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.850483043368194</v>
+        <v>6.524269565112566</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1021523901174284</v>
+        <v>0.1019622408584964</v>
       </c>
       <c r="C23">
-        <v>29.29353953930374</v>
+        <v>29.03308711126552</v>
       </c>
       <c r="D23">
-        <v>31.07261953930374</v>
+        <v>31.16164711126552</v>
       </c>
       <c r="E23">
-        <v>6.49108</v>
+        <v>6.84056</v>
       </c>
       <c r="F23">
-        <v>7.33908</v>
+        <v>7.68856</v>
       </c>
       <c r="G23">
         <v>5.56</v>
@@ -3161,28 +3161,28 @@
         <v>2.6</v>
       </c>
       <c r="M23">
-        <v>0.398512044</v>
+        <v>0.417488808</v>
       </c>
       <c r="N23">
-        <v>2.201487956</v>
+        <v>2.182511192</v>
       </c>
       <c r="O23">
-        <v>0.52835710944</v>
+        <v>0.52380268608</v>
       </c>
       <c r="P23">
-        <v>1.67313084656</v>
+        <v>1.65870850592</v>
       </c>
       <c r="Q23">
-        <v>2.01313084656</v>
+        <v>1.99870850592</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1183368482499094</v>
+        <v>0.1190811293057646</v>
       </c>
       <c r="T23">
-        <v>1.223075469497108</v>
+        <v>1.235625117349076</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.524269565112567</v>
+        <v>6.22771185760745</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1019622408584964</v>
+        <v>0.1019468915995644</v>
       </c>
       <c r="C24">
-        <v>29.03308711126552</v>
+        <v>28.69081586679466</v>
       </c>
       <c r="D24">
-        <v>31.16164711126552</v>
+        <v>31.16885586679466</v>
       </c>
       <c r="E24">
-        <v>6.84056</v>
+        <v>7.190040000000001</v>
       </c>
       <c r="F24">
-        <v>7.68856</v>
+        <v>8.038040000000001</v>
       </c>
       <c r="G24">
         <v>5.56</v>
@@ -3243,45 +3243,45 @@
         <v>2.6</v>
       </c>
       <c r="M24">
-        <v>0.417488808</v>
+        <v>0.444503612</v>
       </c>
       <c r="N24">
-        <v>2.182511192</v>
+        <v>2.155496388</v>
       </c>
       <c r="O24">
-        <v>0.52380268608</v>
+        <v>0.51731913312</v>
       </c>
       <c r="P24">
-        <v>1.65870850592</v>
+        <v>1.63817725488</v>
       </c>
       <c r="Q24">
-        <v>1.99870850592</v>
+        <v>1.97817725488</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1190811293057646</v>
+        <v>0.1198447423370966</v>
       </c>
       <c r="T24">
-        <v>1.235625117349076</v>
+        <v>1.248500730080315</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.22771185760745</v>
+        <v>5.849221310714568</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1019468915995644</v>
+        <v>0.1017643423406324</v>
       </c>
       <c r="C25">
-        <v>28.69081586679466</v>
+        <v>28.42732625729801</v>
       </c>
       <c r="D25">
-        <v>31.16885586679466</v>
+        <v>31.25484625729801</v>
       </c>
       <c r="E25">
-        <v>7.190040000000001</v>
+        <v>7.53952</v>
       </c>
       <c r="F25">
-        <v>8.038040000000001</v>
+        <v>8.38752</v>
       </c>
       <c r="G25">
         <v>5.56</v>
@@ -3325,28 +3325,28 @@
         <v>2.6</v>
       </c>
       <c r="M25">
-        <v>0.444503612</v>
+        <v>0.463829856</v>
       </c>
       <c r="N25">
-        <v>2.155496388</v>
+        <v>2.136170144</v>
       </c>
       <c r="O25">
-        <v>0.51731913312</v>
+        <v>0.51268083456</v>
       </c>
       <c r="P25">
-        <v>1.63817725488</v>
+        <v>1.62348930944</v>
       </c>
       <c r="Q25">
-        <v>1.97817725488</v>
+        <v>1.96348930944</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1198447423370966</v>
+        <v>0.1206284504482005</v>
       </c>
       <c r="T25">
-        <v>1.248500730080315</v>
+        <v>1.261715174725534</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.849221310714568</v>
+        <v>5.605503756101462</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1017643423406324</v>
+        <v>0.1015817930817004</v>
       </c>
       <c r="C26">
-        <v>28.42732625729801</v>
+        <v>28.16431243065765</v>
       </c>
       <c r="D26">
-        <v>31.25484625729801</v>
+        <v>31.34131243065765</v>
       </c>
       <c r="E26">
-        <v>7.53952</v>
+        <v>7.889</v>
       </c>
       <c r="F26">
-        <v>8.38752</v>
+        <v>8.737</v>
       </c>
       <c r="G26">
         <v>5.56</v>
@@ -3407,28 +3407,28 @@
         <v>2.6</v>
       </c>
       <c r="M26">
-        <v>0.463829856</v>
+        <v>0.4831561</v>
       </c>
       <c r="N26">
-        <v>2.136170144</v>
+        <v>2.1168439</v>
       </c>
       <c r="O26">
-        <v>0.51268083456</v>
+        <v>0.508042536</v>
       </c>
       <c r="P26">
-        <v>1.62348930944</v>
+        <v>1.608801364</v>
       </c>
       <c r="Q26">
-        <v>1.96348930944</v>
+        <v>1.948801364</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1206284504482005</v>
+        <v>0.1214330574422672</v>
       </c>
       <c r="T26">
-        <v>1.261715174725534</v>
+        <v>1.275282004561293</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.605503756101462</v>
+        <v>5.381283605857403</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1015817930817004</v>
+        <v>0.1013992438227684</v>
       </c>
       <c r="C27">
-        <v>28.16431243065765</v>
+        <v>27.90177834657147</v>
       </c>
       <c r="D27">
-        <v>31.34131243065765</v>
+        <v>31.42825834657147</v>
       </c>
       <c r="E27">
-        <v>7.889</v>
+        <v>8.238479999999999</v>
       </c>
       <c r="F27">
-        <v>8.737</v>
+        <v>9.08648</v>
       </c>
       <c r="G27">
         <v>5.56</v>
@@ -3489,28 +3489,28 @@
         <v>2.6</v>
       </c>
       <c r="M27">
-        <v>0.4831561</v>
+        <v>0.502482344</v>
       </c>
       <c r="N27">
-        <v>2.1168439</v>
+        <v>2.097517656</v>
       </c>
       <c r="O27">
-        <v>0.508042536</v>
+        <v>0.50340423744</v>
       </c>
       <c r="P27">
-        <v>1.608801364</v>
+        <v>1.59411341856</v>
       </c>
       <c r="Q27">
-        <v>1.948801364</v>
+        <v>1.93411341856</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1214330574422672</v>
+        <v>0.1222594105713086</v>
       </c>
       <c r="T27">
-        <v>1.275282004561293</v>
+        <v>1.289215505473693</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.381283605857403</v>
+        <v>5.174311159478272</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1013992438227684</v>
+        <v>0.1012166945638364</v>
       </c>
       <c r="C28">
-        <v>27.90177834657147</v>
+        <v>27.63972800879897</v>
       </c>
       <c r="D28">
-        <v>31.42825834657147</v>
+        <v>31.51568800879897</v>
       </c>
       <c r="E28">
-        <v>8.238479999999999</v>
+        <v>8.587960000000001</v>
       </c>
       <c r="F28">
-        <v>9.08648</v>
+        <v>9.435960000000001</v>
       </c>
       <c r="G28">
         <v>5.56</v>
@@ -3571,28 +3571,28 @@
         <v>2.6</v>
       </c>
       <c r="M28">
-        <v>0.502482344</v>
+        <v>0.5218085880000001</v>
       </c>
       <c r="N28">
-        <v>2.097517656</v>
+        <v>2.078191412</v>
       </c>
       <c r="O28">
-        <v>0.50340423744</v>
+        <v>0.4987659388799999</v>
       </c>
       <c r="P28">
-        <v>1.59411341856</v>
+        <v>1.57942547312</v>
       </c>
       <c r="Q28">
-        <v>1.93411341856</v>
+        <v>1.91942547312</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1222594105713086</v>
+        <v>0.1231084035121046</v>
       </c>
       <c r="T28">
-        <v>1.289215505473693</v>
+        <v>1.303530746137119</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.174311159478272</v>
+        <v>4.98267000542352</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1012166945638364</v>
+        <v>0.1010341453049044</v>
       </c>
       <c r="C29">
-        <v>27.63972800879897</v>
+        <v>27.37816546577589</v>
       </c>
       <c r="D29">
-        <v>31.51568800879897</v>
+        <v>31.60360546577589</v>
       </c>
       <c r="E29">
-        <v>8.587960000000001</v>
+        <v>8.93744</v>
       </c>
       <c r="F29">
-        <v>9.435960000000001</v>
+        <v>9.785440000000001</v>
       </c>
       <c r="G29">
         <v>5.56</v>
@@ -3653,28 +3653,28 @@
         <v>2.6</v>
       </c>
       <c r="M29">
-        <v>0.5218085880000001</v>
+        <v>0.5411348320000001</v>
       </c>
       <c r="N29">
-        <v>2.078191412</v>
+        <v>2.058865168</v>
       </c>
       <c r="O29">
-        <v>0.4987659388799999</v>
+        <v>0.49412764032</v>
       </c>
       <c r="P29">
-        <v>1.57942547312</v>
+        <v>1.56473752768</v>
       </c>
       <c r="Q29">
-        <v>1.91942547312</v>
+        <v>1.90473752768</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1231084035121046</v>
+        <v>0.123980979590145</v>
       </c>
       <c r="T29">
-        <v>1.303530746137119</v>
+        <v>1.318243632374528</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.98267000542352</v>
+        <v>4.804717505229823</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1010341453049044</v>
+        <v>0.1008515960459724</v>
       </c>
       <c r="C30">
-        <v>27.37816546577589</v>
+        <v>27.11709481123903</v>
       </c>
       <c r="D30">
-        <v>31.60360546577589</v>
+        <v>31.69201481123903</v>
       </c>
       <c r="E30">
-        <v>8.93744</v>
+        <v>9.28692</v>
       </c>
       <c r="F30">
-        <v>9.785440000000001</v>
+        <v>10.13492</v>
       </c>
       <c r="G30">
         <v>5.56</v>
@@ -3735,28 +3735,28 @@
         <v>2.6</v>
       </c>
       <c r="M30">
-        <v>0.5411348320000001</v>
+        <v>0.5604610760000001</v>
       </c>
       <c r="N30">
-        <v>2.058865168</v>
+        <v>2.039538924</v>
       </c>
       <c r="O30">
-        <v>0.49412764032</v>
+        <v>0.48948934176</v>
       </c>
       <c r="P30">
-        <v>1.56473752768</v>
+        <v>1.55004958224</v>
       </c>
       <c r="Q30">
-        <v>1.90473752768</v>
+        <v>1.89004958224</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.123980979590145</v>
+        <v>0.1248781352760175</v>
       </c>
       <c r="T30">
-        <v>1.318243632374528</v>
+        <v>1.333370966111583</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.804717505229823</v>
+        <v>4.639037591256381</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1008515960459724</v>
+        <v>0.1012390467870404</v>
       </c>
       <c r="C31">
-        <v>27.11709481123903</v>
+        <v>26.58055656828302</v>
       </c>
       <c r="D31">
-        <v>31.69201481123903</v>
+        <v>31.50495656828302</v>
       </c>
       <c r="E31">
-        <v>9.286919999999999</v>
+        <v>9.636399999999998</v>
       </c>
       <c r="F31">
-        <v>10.13492</v>
+        <v>10.4844</v>
       </c>
       <c r="G31">
         <v>5.56</v>
@@ -3817,45 +3817,45 @@
         <v>2.6</v>
       </c>
       <c r="M31">
-        <v>0.5604610759999999</v>
+        <v>0.60599832</v>
       </c>
       <c r="N31">
-        <v>2.039538924</v>
+        <v>1.99400168</v>
       </c>
       <c r="O31">
-        <v>0.4894893417600001</v>
+        <v>0.4785604032</v>
       </c>
       <c r="P31">
-        <v>1.55004958224</v>
+        <v>1.5154412768</v>
       </c>
       <c r="Q31">
-        <v>1.89004958224</v>
+        <v>1.8554412768</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1248781352760175</v>
+        <v>0.1258009239814863</v>
       </c>
       <c r="T31">
-        <v>1.333370966111583</v>
+        <v>1.348930509383981</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.639037591256383</v>
+        <v>4.290440937195998</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1012390467870404</v>
+        <v>0.1010754975281084</v>
       </c>
       <c r="C32">
-        <v>26.58055656828302</v>
+        <v>26.30976689723583</v>
       </c>
       <c r="D32">
-        <v>31.50495656828302</v>
+        <v>31.58364689723583</v>
       </c>
       <c r="E32">
-        <v>9.636399999999998</v>
+        <v>9.98588</v>
       </c>
       <c r="F32">
-        <v>10.4844</v>
+        <v>10.83388</v>
       </c>
       <c r="G32">
         <v>5.56</v>
@@ -3899,28 +3899,28 @@
         <v>2.6</v>
       </c>
       <c r="M32">
-        <v>0.60599832</v>
+        <v>0.6261982640000001</v>
       </c>
       <c r="N32">
-        <v>1.99400168</v>
+        <v>1.973801736</v>
       </c>
       <c r="O32">
-        <v>0.4785604032</v>
+        <v>0.47371241664</v>
       </c>
       <c r="P32">
-        <v>1.5154412768</v>
+        <v>1.50008931936</v>
       </c>
       <c r="Q32">
-        <v>1.8554412768</v>
+        <v>1.84008931936</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1258009239814863</v>
+        <v>0.1267504601856643</v>
       </c>
       <c r="T32">
-        <v>1.348930509383981</v>
+        <v>1.364941053910653</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.290440937195998</v>
+        <v>4.152039616641288</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1010754975281084</v>
+        <v>0.1009119482691764</v>
       </c>
       <c r="C33">
-        <v>26.30976689723583</v>
+        <v>26.03937130213922</v>
       </c>
       <c r="D33">
-        <v>31.58364689723583</v>
+        <v>31.66273130213922</v>
       </c>
       <c r="E33">
-        <v>9.98588</v>
+        <v>10.33536</v>
       </c>
       <c r="F33">
-        <v>10.83388</v>
+        <v>11.18336</v>
       </c>
       <c r="G33">
         <v>5.56</v>
@@ -3981,28 +3981,28 @@
         <v>2.6</v>
       </c>
       <c r="M33">
-        <v>0.6261982640000001</v>
+        <v>0.646398208</v>
       </c>
       <c r="N33">
-        <v>1.973801736</v>
+        <v>1.953601792</v>
       </c>
       <c r="O33">
-        <v>0.47371241664</v>
+        <v>0.46886443008</v>
       </c>
       <c r="P33">
-        <v>1.50008931936</v>
+        <v>1.48473736192</v>
       </c>
       <c r="Q33">
-        <v>1.84008931936</v>
+        <v>1.82473736192</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1267504601856643</v>
+        <v>0.1277279239252594</v>
       </c>
       <c r="T33">
-        <v>1.364941053910653</v>
+        <v>1.381422496805756</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.152039616641288</v>
+        <v>4.022288378621248</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1009119482691764</v>
+        <v>0.1016261990102444</v>
       </c>
       <c r="C34">
-        <v>26.03937130213922</v>
+        <v>25.3473951408133</v>
       </c>
       <c r="D34">
-        <v>31.66273130213922</v>
+        <v>31.3202351408133</v>
       </c>
       <c r="E34">
-        <v>10.33536</v>
+        <v>10.68484</v>
       </c>
       <c r="F34">
-        <v>11.18336</v>
+        <v>11.53284</v>
       </c>
       <c r="G34">
         <v>5.56</v>
@@ -4063,45 +4063,45 @@
         <v>2.6</v>
       </c>
       <c r="M34">
-        <v>0.646398208</v>
+        <v>0.7069630920000001</v>
       </c>
       <c r="N34">
-        <v>1.953601792</v>
+        <v>1.893036908</v>
       </c>
       <c r="O34">
-        <v>0.46886443008</v>
+        <v>0.45432885792</v>
       </c>
       <c r="P34">
-        <v>1.48473736192</v>
+        <v>1.43870805008</v>
       </c>
       <c r="Q34">
-        <v>1.82473736192</v>
+        <v>1.77870805008</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1277279239252594</v>
+        <v>0.1287345656869319</v>
       </c>
       <c r="T34">
-        <v>1.381422496805756</v>
+        <v>1.398395923070862</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.24</v>
       </c>
       <c r="W34">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.022288378621248</v>
+        <v>3.677702597804073</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1016261990102444</v>
+        <v>0.1014892497513124</v>
       </c>
       <c r="C35">
-        <v>25.3473951408133</v>
+        <v>25.06300944836656</v>
       </c>
       <c r="D35">
-        <v>31.3202351408133</v>
+        <v>31.38532944836657</v>
       </c>
       <c r="E35">
-        <v>10.68484</v>
+        <v>11.03432</v>
       </c>
       <c r="F35">
-        <v>11.53284</v>
+        <v>11.88232</v>
       </c>
       <c r="G35">
         <v>5.56</v>
@@ -4145,28 +4145,28 @@
         <v>2.6</v>
       </c>
       <c r="M35">
-        <v>0.7069630920000001</v>
+        <v>0.7283862160000001</v>
       </c>
       <c r="N35">
-        <v>1.893036908</v>
+        <v>1.871613784</v>
       </c>
       <c r="O35">
-        <v>0.45432885792</v>
+        <v>0.44918730816</v>
       </c>
       <c r="P35">
-        <v>1.43870805008</v>
+        <v>1.42242647584</v>
       </c>
       <c r="Q35">
-        <v>1.77870805008</v>
+        <v>1.76242647584</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1287345656869319</v>
+        <v>0.1297717117444127</v>
       </c>
       <c r="T35">
-        <v>1.398395923070862</v>
+        <v>1.415883695586426</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.677702597804073</v>
+        <v>3.569534874339247</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1014892497513124</v>
+        <v>0.1020971004923804</v>
       </c>
       <c r="C36">
-        <v>25.06300944836656</v>
+        <v>24.42665355533623</v>
       </c>
       <c r="D36">
-        <v>31.38532944836657</v>
+        <v>31.09845355533623</v>
       </c>
       <c r="E36">
-        <v>11.03432</v>
+        <v>11.3838</v>
       </c>
       <c r="F36">
-        <v>11.88232</v>
+        <v>12.2318</v>
       </c>
       <c r="G36">
         <v>5.56</v>
@@ -4227,45 +4227,45 @@
         <v>2.6</v>
       </c>
       <c r="M36">
-        <v>0.7283862160000001</v>
+        <v>0.7840583800000002</v>
       </c>
       <c r="N36">
-        <v>1.871613784</v>
+        <v>1.81594162</v>
       </c>
       <c r="O36">
-        <v>0.44918730816</v>
+        <v>0.4358259888</v>
       </c>
       <c r="P36">
-        <v>1.42242647584</v>
+        <v>1.3801156312</v>
       </c>
       <c r="Q36">
-        <v>1.76242647584</v>
+        <v>1.7201156312</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1297717117444127</v>
+        <v>0.1308407699882775</v>
       </c>
       <c r="T36">
-        <v>1.415883695586426</v>
+        <v>1.433909553410161</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.569534874339247</v>
+        <v>3.316079601113376</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1020971004923804</v>
+        <v>0.1019814312334484</v>
       </c>
       <c r="C37">
-        <v>24.42665355533623</v>
+        <v>24.13135907080483</v>
       </c>
       <c r="D37">
-        <v>31.09845355533623</v>
+        <v>31.15263907080483</v>
       </c>
       <c r="E37">
-        <v>11.3838</v>
+        <v>11.73328</v>
       </c>
       <c r="F37">
-        <v>12.2318</v>
+        <v>12.58128</v>
       </c>
       <c r="G37">
         <v>5.56</v>
@@ -4309,28 +4309,28 @@
         <v>2.6</v>
       </c>
       <c r="M37">
-        <v>0.7840583800000002</v>
+        <v>0.8064600480000002</v>
       </c>
       <c r="N37">
-        <v>1.81594162</v>
+        <v>1.793539952</v>
       </c>
       <c r="O37">
-        <v>0.4358259888</v>
+        <v>0.43044958848</v>
       </c>
       <c r="P37">
-        <v>1.3801156312</v>
+        <v>1.36309036352</v>
       </c>
       <c r="Q37">
-        <v>1.7201156312</v>
+        <v>1.70309036352</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1308407699882775</v>
+        <v>0.1319432363022631</v>
       </c>
       <c r="T37">
-        <v>1.433909553410161</v>
+        <v>1.452498719290888</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.316079601113376</v>
+        <v>3.223966278860226</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1019814312334484</v>
+        <v>0.1018657619745164</v>
       </c>
       <c r="C38">
-        <v>24.13135907080483</v>
+        <v>23.83625374003817</v>
       </c>
       <c r="D38">
-        <v>31.15263907080483</v>
+        <v>31.20701374003817</v>
       </c>
       <c r="E38">
-        <v>11.73328</v>
+        <v>12.08276</v>
       </c>
       <c r="F38">
-        <v>12.58128</v>
+        <v>12.93076</v>
       </c>
       <c r="G38">
         <v>5.56</v>
@@ -4391,28 +4391,28 @@
         <v>2.6</v>
       </c>
       <c r="M38">
-        <v>0.806460048</v>
+        <v>0.828861716</v>
       </c>
       <c r="N38">
-        <v>1.793539952</v>
+        <v>1.771138284</v>
       </c>
       <c r="O38">
-        <v>0.43044958848</v>
+        <v>0.42507318816</v>
       </c>
       <c r="P38">
-        <v>1.36309036352</v>
+        <v>1.34606509584</v>
       </c>
       <c r="Q38">
-        <v>1.70309036352</v>
+        <v>1.68606509584</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1319432363022631</v>
+        <v>0.1330807015468514</v>
       </c>
       <c r="T38">
-        <v>1.452498719290887</v>
+        <v>1.471678017421796</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.223966278860227</v>
+        <v>3.136832055107248</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1018657619745164</v>
+        <v>0.1017500927155844</v>
       </c>
       <c r="C39">
-        <v>23.83625374003817</v>
+        <v>23.54133855523054</v>
       </c>
       <c r="D39">
-        <v>31.20701374003817</v>
+        <v>31.26157855523054</v>
       </c>
       <c r="E39">
-        <v>12.08276</v>
+        <v>12.43224</v>
       </c>
       <c r="F39">
-        <v>12.93076</v>
+        <v>13.28024</v>
       </c>
       <c r="G39">
         <v>5.56</v>
@@ -4473,28 +4473,28 @@
         <v>2.6</v>
       </c>
       <c r="M39">
-        <v>0.828861716</v>
+        <v>0.8512633840000001</v>
       </c>
       <c r="N39">
-        <v>1.771138284</v>
+        <v>1.748736616</v>
       </c>
       <c r="O39">
-        <v>0.42507318816</v>
+        <v>0.41969678784</v>
       </c>
       <c r="P39">
-        <v>1.34606509584</v>
+        <v>1.32903982816</v>
       </c>
       <c r="Q39">
-        <v>1.68606509584</v>
+        <v>1.66903982816</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1330807015468514</v>
+        <v>0.1342548592186845</v>
       </c>
       <c r="T39">
-        <v>1.471678017421796</v>
+        <v>1.491476002589185</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.136832055107248</v>
+        <v>3.054283843130741</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1017500927155844</v>
+        <v>0.1039463434566524</v>
       </c>
       <c r="C40">
-        <v>23.54133855523054</v>
+        <v>22.18735520613318</v>
       </c>
       <c r="D40">
-        <v>31.26157855523054</v>
+        <v>30.25707520613318</v>
       </c>
       <c r="E40">
-        <v>12.43224</v>
+        <v>12.78172</v>
       </c>
       <c r="F40">
-        <v>13.28024</v>
+        <v>13.62972</v>
       </c>
       <c r="G40">
         <v>5.56</v>
@@ -4555,45 +4555,45 @@
         <v>2.6</v>
       </c>
       <c r="M40">
-        <v>0.8512633840000001</v>
+        <v>0.9799768680000002</v>
       </c>
       <c r="N40">
-        <v>1.748736616</v>
+        <v>1.620023132</v>
       </c>
       <c r="O40">
-        <v>0.41969678784</v>
+        <v>0.38880555168</v>
       </c>
       <c r="P40">
-        <v>1.32903982816</v>
+        <v>1.23121758032</v>
       </c>
       <c r="Q40">
-        <v>1.66903982816</v>
+        <v>1.57121758032</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1342548592186845</v>
+        <v>0.1354675138633646</v>
       </c>
       <c r="T40">
-        <v>1.491476002589185</v>
+        <v>1.511923102024358</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.24</v>
       </c>
       <c r="W40">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.054283843130741</v>
+        <v>2.65312384904171</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1039463434566524</v>
+        <v>0.1038899541977204</v>
       </c>
       <c r="C41">
-        <v>22.18735520613318</v>
+        <v>21.8628579616276</v>
       </c>
       <c r="D41">
-        <v>30.25707520613318</v>
+        <v>30.28205796162759</v>
       </c>
       <c r="E41">
-        <v>12.78172</v>
+        <v>13.1312</v>
       </c>
       <c r="F41">
-        <v>13.62972</v>
+        <v>13.9792</v>
       </c>
       <c r="G41">
         <v>5.56</v>
@@ -4637,28 +4637,28 @@
         <v>2.6</v>
       </c>
       <c r="M41">
-        <v>0.9799768680000002</v>
+        <v>1.00510448</v>
       </c>
       <c r="N41">
-        <v>1.620023132</v>
+        <v>1.59489552</v>
       </c>
       <c r="O41">
-        <v>0.38880555168</v>
+        <v>0.3827749248</v>
       </c>
       <c r="P41">
-        <v>1.23121758032</v>
+        <v>1.2121205952</v>
       </c>
       <c r="Q41">
-        <v>1.57121758032</v>
+        <v>1.5521205952</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1354675138633646</v>
+        <v>0.136720590329534</v>
       </c>
       <c r="T41">
-        <v>1.511923102024358</v>
+        <v>1.533051771440703</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.65312384904171</v>
+        <v>2.586795752815667</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1038899541977204</v>
+        <v>0.1038335649387884</v>
       </c>
       <c r="C42">
-        <v>21.8628579616276</v>
+        <v>21.53840200689202</v>
       </c>
       <c r="D42">
-        <v>30.28205796162759</v>
+        <v>30.30708200689202</v>
       </c>
       <c r="E42">
-        <v>13.1312</v>
+        <v>13.48068</v>
       </c>
       <c r="F42">
-        <v>13.9792</v>
+        <v>14.32868</v>
       </c>
       <c r="G42">
         <v>5.56</v>
@@ -4719,28 +4719,28 @@
         <v>2.6</v>
       </c>
       <c r="M42">
-        <v>1.00510448</v>
+        <v>1.030232092</v>
       </c>
       <c r="N42">
-        <v>1.59489552</v>
+        <v>1.569767908</v>
       </c>
       <c r="O42">
-        <v>0.3827749248</v>
+        <v>0.3767442979199999</v>
       </c>
       <c r="P42">
-        <v>1.2121205952</v>
+        <v>1.19302361008</v>
       </c>
       <c r="Q42">
-        <v>1.5521205952</v>
+        <v>1.53302361008</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.136720590329534</v>
+        <v>0.1380161439640481</v>
       </c>
       <c r="T42">
-        <v>1.533051771440703</v>
+        <v>1.554896666938958</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.586795752815667</v>
+        <v>2.523703173478699</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1038335649387884</v>
+        <v>0.1050220556798564</v>
       </c>
       <c r="C43">
-        <v>21.53840200689202</v>
+        <v>20.67010200468916</v>
       </c>
       <c r="D43">
-        <v>30.30708200689202</v>
+        <v>29.78826200468916</v>
       </c>
       <c r="E43">
-        <v>13.48068</v>
+        <v>13.83016</v>
       </c>
       <c r="F43">
-        <v>14.32868</v>
+        <v>14.67816</v>
       </c>
       <c r="G43">
         <v>5.56</v>
@@ -4801,45 +4801,45 @@
         <v>2.6</v>
       </c>
       <c r="M43">
-        <v>1.030232092</v>
+        <v>1.112604528</v>
       </c>
       <c r="N43">
-        <v>1.569767908</v>
+        <v>1.487395472</v>
       </c>
       <c r="O43">
-        <v>0.3767442979199999</v>
+        <v>0.3569749132799999</v>
       </c>
       <c r="P43">
-        <v>1.19302361008</v>
+        <v>1.13042055872</v>
       </c>
       <c r="Q43">
-        <v>1.53302361008</v>
+        <v>1.47042055872</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1380161439640481</v>
+        <v>0.1393563718618213</v>
       </c>
       <c r="T43">
-        <v>1.554896666938958</v>
+        <v>1.577494834695774</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.24</v>
       </c>
       <c r="W43">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.523703173478699</v>
+        <v>2.336859085657073</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1050220556798564</v>
+        <v>0.1049953064209244</v>
       </c>
       <c r="C44">
-        <v>20.67010200468916</v>
+        <v>20.33210356908702</v>
       </c>
       <c r="D44">
-        <v>29.78826200468916</v>
+        <v>29.79974356908702</v>
       </c>
       <c r="E44">
-        <v>13.83016</v>
+        <v>14.17964</v>
       </c>
       <c r="F44">
-        <v>14.67816</v>
+        <v>15.02764</v>
       </c>
       <c r="G44">
         <v>5.56</v>
@@ -4883,28 +4883,28 @@
         <v>2.6</v>
       </c>
       <c r="M44">
-        <v>1.112604528</v>
+        <v>1.139095112</v>
       </c>
       <c r="N44">
-        <v>1.487395472</v>
+        <v>1.460904888</v>
       </c>
       <c r="O44">
-        <v>0.35697491328</v>
+        <v>0.35061717312</v>
       </c>
       <c r="P44">
-        <v>1.13042055872</v>
+        <v>1.11028771488</v>
       </c>
       <c r="Q44">
-        <v>1.47042055872</v>
+        <v>1.45028771488</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1393563718618213</v>
+        <v>0.1407436252998673</v>
       </c>
       <c r="T44">
-        <v>1.577494834695774</v>
+        <v>1.600885920619495</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.336859085657073</v>
+        <v>2.282513525525514</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1049953064209244</v>
+        <v>0.1049685571619924</v>
       </c>
       <c r="C45">
-        <v>20.33210356908702</v>
+        <v>19.99411398778808</v>
       </c>
       <c r="D45">
-        <v>29.79974356908702</v>
+        <v>29.81123398778807</v>
       </c>
       <c r="E45">
-        <v>14.17964</v>
+        <v>14.52912</v>
       </c>
       <c r="F45">
-        <v>15.02764</v>
+        <v>15.37712</v>
       </c>
       <c r="G45">
         <v>5.56</v>
@@ -4965,28 +4965,28 @@
         <v>2.6</v>
       </c>
       <c r="M45">
-        <v>1.139095112</v>
+        <v>1.165585696</v>
       </c>
       <c r="N45">
-        <v>1.460904888</v>
+        <v>1.434414304</v>
       </c>
       <c r="O45">
-        <v>0.35061717312</v>
+        <v>0.3442594329599999</v>
       </c>
       <c r="P45">
-        <v>1.11028771488</v>
+        <v>1.09015487104</v>
       </c>
       <c r="Q45">
-        <v>1.45028771488</v>
+        <v>1.43015487104</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1407436252998673</v>
+        <v>0.1421804235035578</v>
       </c>
       <c r="T45">
-        <v>1.600885920619495</v>
+        <v>1.625112402469064</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.282513525525514</v>
+        <v>2.230638218127206</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1049685571619924</v>
+        <v>0.1049418079030604</v>
       </c>
       <c r="C46">
-        <v>19.99411398778808</v>
+        <v>19.6561332710386</v>
       </c>
       <c r="D46">
-        <v>29.81123398778807</v>
+        <v>29.8227332710386</v>
       </c>
       <c r="E46">
-        <v>14.52912</v>
+        <v>14.8786</v>
       </c>
       <c r="F46">
-        <v>15.37712</v>
+        <v>15.7266</v>
       </c>
       <c r="G46">
         <v>5.56</v>
@@ -5047,28 +5047,28 @@
         <v>2.6</v>
       </c>
       <c r="M46">
-        <v>1.165585696</v>
+        <v>1.19207628</v>
       </c>
       <c r="N46">
-        <v>1.434414304</v>
+        <v>1.40792372</v>
       </c>
       <c r="O46">
-        <v>0.3442594329599999</v>
+        <v>0.3379016927999999</v>
       </c>
       <c r="P46">
-        <v>1.09015487104</v>
+        <v>1.0700220272</v>
       </c>
       <c r="Q46">
-        <v>1.43015487104</v>
+        <v>1.4100220272</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1421804235035578</v>
+        <v>0.1436694689146552</v>
       </c>
       <c r="T46">
-        <v>1.625112402469064</v>
+        <v>1.650219847294981</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.230638218127206</v>
+        <v>2.181068479946602</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1049418079030604</v>
+        <v>0.1049150586441284</v>
       </c>
       <c r="C47">
-        <v>19.6561332710386</v>
+        <v>19.31816142910069</v>
       </c>
       <c r="D47">
-        <v>29.8227332710386</v>
+        <v>29.83424142910069</v>
       </c>
       <c r="E47">
-        <v>14.8786</v>
+        <v>15.22808</v>
       </c>
       <c r="F47">
-        <v>15.7266</v>
+        <v>16.07608</v>
       </c>
       <c r="G47">
         <v>5.56</v>
@@ -5129,28 +5129,28 @@
         <v>2.6</v>
       </c>
       <c r="M47">
-        <v>1.19207628</v>
+        <v>1.218566864</v>
       </c>
       <c r="N47">
-        <v>1.40792372</v>
+        <v>1.381433136</v>
       </c>
       <c r="O47">
-        <v>0.3379016927999999</v>
+        <v>0.33154395264</v>
       </c>
       <c r="P47">
-        <v>1.0700220272</v>
+        <v>1.04988918336</v>
       </c>
       <c r="Q47">
-        <v>1.4100220272</v>
+        <v>1.38988918336</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1436694689146552</v>
+        <v>0.1452136641557933</v>
       </c>
       <c r="T47">
-        <v>1.650219847294981</v>
+        <v>1.67625719748482</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.181068479946602</v>
+        <v>2.133653947773849</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1049150586441284</v>
+        <v>0.1048883093851964</v>
       </c>
       <c r="C48">
-        <v>19.31816142910069</v>
+        <v>18.98019847225233</v>
       </c>
       <c r="D48">
-        <v>29.83424142910069</v>
+        <v>29.84575847225233</v>
       </c>
       <c r="E48">
-        <v>15.22808</v>
+        <v>15.57756</v>
       </c>
       <c r="F48">
-        <v>16.07608</v>
+        <v>16.42556</v>
       </c>
       <c r="G48">
         <v>5.56</v>
@@ -5211,28 +5211,28 @@
         <v>2.6</v>
       </c>
       <c r="M48">
-        <v>1.218566864</v>
+        <v>1.245057448</v>
       </c>
       <c r="N48">
-        <v>1.381433136</v>
+        <v>1.354942552</v>
       </c>
       <c r="O48">
-        <v>0.33154395264</v>
+        <v>0.32518621248</v>
       </c>
       <c r="P48">
-        <v>1.04988918336</v>
+        <v>1.02975633952</v>
       </c>
       <c r="Q48">
-        <v>1.38988918336</v>
+        <v>1.36975633952</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1452136641557933</v>
+        <v>0.1468161309154648</v>
       </c>
       <c r="T48">
-        <v>1.67625719748482</v>
+        <v>1.703277089191257</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.133653947773849</v>
+        <v>2.088257055268024</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1048883093851964</v>
+        <v>0.1048615601262644</v>
       </c>
       <c r="C49">
-        <v>18.98019847225233</v>
+        <v>18.6422444107873</v>
       </c>
       <c r="D49">
-        <v>29.84575847225233</v>
+        <v>29.8572844107873</v>
       </c>
       <c r="E49">
-        <v>15.57756</v>
+        <v>15.92704</v>
       </c>
       <c r="F49">
-        <v>16.42556</v>
+        <v>16.77504</v>
       </c>
       <c r="G49">
         <v>5.56</v>
@@ -5293,28 +5293,28 @@
         <v>2.6</v>
       </c>
       <c r="M49">
-        <v>1.245057448</v>
+        <v>1.271548032</v>
       </c>
       <c r="N49">
-        <v>1.354942552</v>
+        <v>1.328451968</v>
       </c>
       <c r="O49">
-        <v>0.32518621248</v>
+        <v>0.31882847232</v>
       </c>
       <c r="P49">
-        <v>1.02975633952</v>
+        <v>1.00962349568</v>
       </c>
       <c r="Q49">
-        <v>1.36975633952</v>
+        <v>1.34962349568</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1468161309154648</v>
+        <v>0.1484802310120469</v>
       </c>
       <c r="T49">
-        <v>1.703277089191257</v>
+        <v>1.731336207501788</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.088257055268024</v>
+        <v>2.04475169994994</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1048615601262644</v>
+        <v>0.1048348108673324</v>
       </c>
       <c r="C50">
-        <v>18.64224441078731</v>
+        <v>18.30429925501537</v>
       </c>
       <c r="D50">
-        <v>29.85728441078731</v>
+        <v>29.86881925501537</v>
       </c>
       <c r="E50">
-        <v>15.92704</v>
+        <v>16.27652</v>
       </c>
       <c r="F50">
-        <v>16.77504</v>
+        <v>17.12452</v>
       </c>
       <c r="G50">
         <v>5.56</v>
@@ -5375,28 +5375,28 @@
         <v>2.6</v>
       </c>
       <c r="M50">
-        <v>1.271548032</v>
+        <v>1.298038616</v>
       </c>
       <c r="N50">
-        <v>1.328451968</v>
+        <v>1.301961384</v>
       </c>
       <c r="O50">
-        <v>0.31882847232</v>
+        <v>0.31247073216</v>
       </c>
       <c r="P50">
-        <v>1.00962349568</v>
+        <v>0.98949065184</v>
       </c>
       <c r="Q50">
-        <v>1.34962349568</v>
+        <v>1.32949065184</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1484802310120469</v>
+        <v>0.1502095899359458</v>
       </c>
       <c r="T50">
-        <v>1.731336207501788</v>
+        <v>1.760495683393124</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.04475169994994</v>
+        <v>2.003022073420349</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1048348108673324</v>
+        <v>0.1102040616084004</v>
       </c>
       <c r="C51">
-        <v>18.30429925501537</v>
+        <v>15.80528034591141</v>
       </c>
       <c r="D51">
-        <v>29.86881925501537</v>
+        <v>27.71928034591141</v>
       </c>
       <c r="E51">
-        <v>16.27652</v>
+        <v>16.626</v>
       </c>
       <c r="F51">
-        <v>17.12452</v>
+        <v>17.474</v>
       </c>
       <c r="G51">
         <v>5.56</v>
@@ -5457,45 +5457,45 @@
         <v>2.6</v>
       </c>
       <c r="M51">
-        <v>1.298038616</v>
+        <v>1.57266</v>
       </c>
       <c r="N51">
-        <v>1.301961384</v>
+        <v>1.02734</v>
       </c>
       <c r="O51">
-        <v>0.31247073216</v>
+        <v>0.2465616</v>
       </c>
       <c r="P51">
-        <v>0.98949065184</v>
+        <v>0.7807784000000001</v>
       </c>
       <c r="Q51">
-        <v>1.32949065184</v>
+        <v>1.1207784</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1502095899359458</v>
+        <v>0.1520081232168007</v>
       </c>
       <c r="T51">
-        <v>1.760495683393124</v>
+        <v>1.790821538320113</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.003022073420349</v>
+        <v>1.653249907799525</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1102040616084004</v>
+        <v>0.1102852323494684</v>
       </c>
       <c r="C52">
-        <v>15.80528034591141</v>
+        <v>15.42567564154195</v>
       </c>
       <c r="D52">
-        <v>27.71928034591141</v>
+        <v>27.68915564154194</v>
       </c>
       <c r="E52">
-        <v>16.626</v>
+        <v>16.97548</v>
       </c>
       <c r="F52">
-        <v>17.474</v>
+        <v>17.82348</v>
       </c>
       <c r="G52">
         <v>5.56</v>
@@ -5539,28 +5539,28 @@
         <v>2.6</v>
       </c>
       <c r="M52">
-        <v>1.57266</v>
+        <v>1.6041132</v>
       </c>
       <c r="N52">
-        <v>1.02734</v>
+        <v>0.9958868000000001</v>
       </c>
       <c r="O52">
-        <v>0.2465616</v>
+        <v>0.239012832</v>
       </c>
       <c r="P52">
-        <v>0.7807784000000001</v>
+        <v>0.7568739680000001</v>
       </c>
       <c r="Q52">
-        <v>1.1207784</v>
+        <v>1.096873968</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1520081232168007</v>
+        <v>0.1538800660193232</v>
       </c>
       <c r="T52">
-        <v>1.790821538320113</v>
+        <v>1.822385183244123</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.653249907799525</v>
+        <v>1.62083324294071</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1102852323494684</v>
+        <v>0.1103664030905364</v>
       </c>
       <c r="C53">
-        <v>15.42567564154195</v>
+        <v>15.04613634382259</v>
       </c>
       <c r="D53">
-        <v>27.68915564154194</v>
+        <v>27.65909634382259</v>
       </c>
       <c r="E53">
-        <v>16.97548</v>
+        <v>17.32496</v>
       </c>
       <c r="F53">
-        <v>17.82348</v>
+        <v>18.17296</v>
       </c>
       <c r="G53">
         <v>5.56</v>
@@ -5621,28 +5621,28 @@
         <v>2.6</v>
       </c>
       <c r="M53">
-        <v>1.6041132</v>
+        <v>1.6355664</v>
       </c>
       <c r="N53">
-        <v>0.9958868000000001</v>
+        <v>0.9644336000000002</v>
       </c>
       <c r="O53">
-        <v>0.239012832</v>
+        <v>0.2314640640000001</v>
       </c>
       <c r="P53">
-        <v>0.7568739680000001</v>
+        <v>0.7329695360000001</v>
       </c>
       <c r="Q53">
-        <v>1.096873968</v>
+        <v>1.072969536</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1538800660193232</v>
+        <v>0.1558300064386174</v>
       </c>
       <c r="T53">
-        <v>1.822385183244123</v>
+        <v>1.855263980039966</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.62083324294071</v>
+        <v>1.589663372884158</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1103664030905364</v>
+        <v>0.1104475738316044</v>
       </c>
       <c r="C54">
-        <v>15.04613634382259</v>
+        <v>14.66666223996831</v>
       </c>
       <c r="D54">
-        <v>27.65909634382259</v>
+        <v>27.6291022399683</v>
       </c>
       <c r="E54">
-        <v>17.32496</v>
+        <v>17.67444</v>
       </c>
       <c r="F54">
-        <v>18.17296</v>
+        <v>18.52244</v>
       </c>
       <c r="G54">
         <v>5.56</v>
@@ -5703,28 +5703,28 @@
         <v>2.6</v>
       </c>
       <c r="M54">
-        <v>1.6355664</v>
+        <v>1.6670196</v>
       </c>
       <c r="N54">
-        <v>0.9644336000000002</v>
+        <v>0.9329804000000002</v>
       </c>
       <c r="O54">
-        <v>0.2314640640000001</v>
+        <v>0.223915296</v>
       </c>
       <c r="P54">
-        <v>0.7329695360000001</v>
+        <v>0.7090651040000001</v>
       </c>
       <c r="Q54">
-        <v>1.072969536</v>
+        <v>1.049065104</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1558300064386174</v>
+        <v>0.1578629230459667</v>
       </c>
       <c r="T54">
-        <v>1.855263980039966</v>
+        <v>1.889541874571802</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.589663372884158</v>
+        <v>1.559669724339174</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1104475738316044</v>
+        <v>0.1105287445726724</v>
       </c>
       <c r="C55">
-        <v>14.66666223996831</v>
+        <v>14.28725311811606</v>
       </c>
       <c r="D55">
-        <v>27.6291022399683</v>
+        <v>27.59917311811606</v>
       </c>
       <c r="E55">
-        <v>17.67444</v>
+        <v>18.02392</v>
       </c>
       <c r="F55">
-        <v>18.52244</v>
+        <v>18.87192</v>
       </c>
       <c r="G55">
         <v>5.56</v>
@@ -5785,28 +5785,28 @@
         <v>2.6</v>
       </c>
       <c r="M55">
-        <v>1.6670196</v>
+        <v>1.6984728</v>
       </c>
       <c r="N55">
-        <v>0.9329804000000002</v>
+        <v>0.9015271999999999</v>
       </c>
       <c r="O55">
-        <v>0.223915296</v>
+        <v>0.2163665279999999</v>
       </c>
       <c r="P55">
-        <v>0.7090651040000001</v>
+        <v>0.6851606719999999</v>
       </c>
       <c r="Q55">
-        <v>1.049065104</v>
+        <v>1.025160672</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1578629230459667</v>
+        <v>0.1599842273318964</v>
       </c>
       <c r="T55">
-        <v>1.889541874571802</v>
+        <v>1.925310112344153</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.559669724339174</v>
+        <v>1.530786951666226</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1105287445726724</v>
+        <v>0.1106099153137404</v>
       </c>
       <c r="C56">
-        <v>14.28725311811606</v>
+        <v>13.90790876731984</v>
       </c>
       <c r="D56">
-        <v>27.59917311811606</v>
+        <v>27.56930876731984</v>
       </c>
       <c r="E56">
-        <v>18.02392</v>
+        <v>18.3734</v>
       </c>
       <c r="F56">
-        <v>18.87192</v>
+        <v>19.2214</v>
       </c>
       <c r="G56">
         <v>5.56</v>
@@ -5867,28 +5867,28 @@
         <v>2.6</v>
       </c>
       <c r="M56">
-        <v>1.6984728</v>
+        <v>1.729926</v>
       </c>
       <c r="N56">
-        <v>0.9015271999999999</v>
+        <v>0.870074</v>
       </c>
       <c r="O56">
-        <v>0.2163665279999999</v>
+        <v>0.20881776</v>
       </c>
       <c r="P56">
-        <v>0.6851606719999999</v>
+        <v>0.6612562400000001</v>
       </c>
       <c r="Q56">
-        <v>1.025160672</v>
+        <v>1.00125624</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1599842273318964</v>
+        <v>0.1621998118083119</v>
       </c>
       <c r="T56">
-        <v>1.925310112344153</v>
+        <v>1.962668049573054</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.530786951666226</v>
+        <v>1.502954461635931</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1106099153137404</v>
+        <v>0.1375106754459153</v>
       </c>
       <c r="C57">
-        <v>13.90790876731984</v>
+        <v>6.281414760803841</v>
       </c>
       <c r="D57">
-        <v>27.56930876731984</v>
+        <v>20.29229476080384</v>
       </c>
       <c r="E57">
-        <v>18.3734</v>
+        <v>18.72288</v>
       </c>
       <c r="F57">
-        <v>19.2214</v>
+        <v>19.57088</v>
       </c>
       <c r="G57">
         <v>5.56</v>
@@ -5949,45 +5949,45 @@
         <v>2.6</v>
       </c>
       <c r="M57">
-        <v>1.729926</v>
+        <v>2.873005184000001</v>
       </c>
       <c r="N57">
-        <v>0.870074</v>
+        <v>-0.2730051840000005</v>
       </c>
       <c r="O57">
-        <v>0.20881776</v>
+        <v>-0.06552124416000012</v>
       </c>
       <c r="P57">
-        <v>0.6612562400000001</v>
+        <v>-0.2074839398400004</v>
       </c>
       <c r="Q57">
-        <v>1.00125624</v>
+        <v>0.1325160601599996</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1621998118083119</v>
+        <v>0.1662676692048867</v>
       </c>
       <c r="T57">
-        <v>1.962668049573054</v>
+        <v>2.031257969251143</v>
       </c>
       <c r="U57">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.24</v>
+        <v>0.217194178233686</v>
       </c>
       <c r="W57">
-        <v>0.0684</v>
+        <v>0.1149158946352949</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.502954461635931</v>
+        <v>0.9049757426403584</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1375106754459153</v>
+        <v>0.1385206754459153</v>
       </c>
       <c r="C58">
-        <v>6.281414760803841</v>
+        <v>5.732806664517465</v>
       </c>
       <c r="D58">
-        <v>20.29229476080384</v>
+        <v>20.09316666451747</v>
       </c>
       <c r="E58">
-        <v>18.72288</v>
+        <v>19.07236</v>
       </c>
       <c r="F58">
-        <v>19.57088</v>
+        <v>19.92036</v>
       </c>
       <c r="G58">
         <v>5.56</v>
@@ -6031,37 +6031,37 @@
         <v>2.6</v>
       </c>
       <c r="M58">
-        <v>2.873005184000001</v>
+        <v>2.924308848000001</v>
       </c>
       <c r="N58">
-        <v>-0.2730051840000005</v>
+        <v>-0.3243088480000007</v>
       </c>
       <c r="O58">
-        <v>-0.06552124416000012</v>
+        <v>-0.07783412352000017</v>
       </c>
       <c r="P58">
-        <v>-0.2074839398400004</v>
+        <v>-0.2464747244800005</v>
       </c>
       <c r="Q58">
-        <v>0.1325160601599996</v>
+        <v>0.09352527551999951</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1662676692048867</v>
+        <v>0.1690692429073259</v>
       </c>
       <c r="T58">
-        <v>2.031257969251143</v>
+        <v>2.078496526675588</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.217194178233686</v>
+        <v>0.2133837540541476</v>
       </c>
       <c r="W58">
-        <v>0.1149158946352949</v>
+        <v>0.1154752649048511</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9049757426403584</v>
+        <v>0.8890989752256152</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1385206754459153</v>
+        <v>0.1395306754459153</v>
       </c>
       <c r="C59">
-        <v>5.732806664517465</v>
+        <v>5.188068675154085</v>
       </c>
       <c r="D59">
-        <v>20.09316666451747</v>
+        <v>19.89790867515409</v>
       </c>
       <c r="E59">
-        <v>19.07236</v>
+        <v>19.42184</v>
       </c>
       <c r="F59">
-        <v>19.92036</v>
+        <v>20.26984</v>
       </c>
       <c r="G59">
         <v>5.56</v>
@@ -6113,37 +6113,37 @@
         <v>2.6</v>
       </c>
       <c r="M59">
-        <v>2.924308848000001</v>
+        <v>2.975612512000001</v>
       </c>
       <c r="N59">
-        <v>-0.3243088480000007</v>
+        <v>-0.3756125120000005</v>
       </c>
       <c r="O59">
-        <v>-0.07783412352000017</v>
+        <v>-0.0901470028800001</v>
       </c>
       <c r="P59">
-        <v>-0.2464747244800005</v>
+        <v>-0.2854655091200003</v>
       </c>
       <c r="Q59">
-        <v>0.09352527551999951</v>
+        <v>0.05453449087999968</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1690692429073259</v>
+        <v>0.1720042248813099</v>
       </c>
       <c r="T59">
-        <v>2.078496526675588</v>
+        <v>2.127984539215483</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2133837540541476</v>
+        <v>0.2097047238118347</v>
       </c>
       <c r="W59">
-        <v>0.1154752649048511</v>
+        <v>0.1160153465444227</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8890989752256152</v>
+        <v>0.8737696825493115</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1395306754459153</v>
+        <v>0.1405406754459153</v>
       </c>
       <c r="C60">
-        <v>5.188068675154089</v>
+        <v>4.647089053733094</v>
       </c>
       <c r="D60">
-        <v>19.89790867515409</v>
+        <v>19.70640905373309</v>
       </c>
       <c r="E60">
-        <v>19.42184</v>
+        <v>19.77132</v>
       </c>
       <c r="F60">
-        <v>20.26984</v>
+        <v>20.61932</v>
       </c>
       <c r="G60">
         <v>5.56</v>
@@ -6195,37 +6195,37 @@
         <v>2.6</v>
       </c>
       <c r="M60">
-        <v>2.975612512</v>
+        <v>3.026916176</v>
       </c>
       <c r="N60">
-        <v>-0.375612512</v>
+        <v>-0.4269161759999998</v>
       </c>
       <c r="O60">
-        <v>-0.09014700287999999</v>
+        <v>-0.1024598822399999</v>
       </c>
       <c r="P60">
-        <v>-0.28546550912</v>
+        <v>-0.3244562937599998</v>
       </c>
       <c r="Q60">
-        <v>0.05453449088000001</v>
+        <v>0.01554370624000018</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1720042248813099</v>
+        <v>0.1750823767076833</v>
       </c>
       <c r="T60">
-        <v>2.127984539215483</v>
+        <v>2.179886601147567</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2097047238118348</v>
+        <v>0.2061504064590919</v>
       </c>
       <c r="W60">
-        <v>0.1160153465444227</v>
+        <v>0.1165371203318053</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8737696825493118</v>
+        <v>0.8589600269128828</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1405406754459153</v>
+        <v>0.1415506754459153</v>
       </c>
       <c r="C61">
-        <v>4.647089053733094</v>
+        <v>4.109760321821927</v>
       </c>
       <c r="D61">
-        <v>19.70640905373309</v>
+        <v>19.51856032182193</v>
       </c>
       <c r="E61">
-        <v>19.77132</v>
+        <v>20.1208</v>
       </c>
       <c r="F61">
-        <v>20.61932</v>
+        <v>20.9688</v>
       </c>
       <c r="G61">
         <v>5.56</v>
@@ -6277,37 +6277,37 @@
         <v>2.6</v>
       </c>
       <c r="M61">
-        <v>3.026916176</v>
+        <v>3.07821984</v>
       </c>
       <c r="N61">
-        <v>-0.4269161759999998</v>
+        <v>-0.47821984</v>
       </c>
       <c r="O61">
-        <v>-0.1024598822399999</v>
+        <v>-0.1147727616</v>
       </c>
       <c r="P61">
-        <v>-0.3244562937599998</v>
+        <v>-0.3634470784</v>
       </c>
       <c r="Q61">
-        <v>0.01554370624000018</v>
+        <v>-0.02344707839999993</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1750823767076833</v>
+        <v>0.1783144361253754</v>
       </c>
       <c r="T61">
-        <v>2.179886601147567</v>
+        <v>2.234383766176256</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2061504064590919</v>
+        <v>0.2027145663514403</v>
       </c>
       <c r="W61">
-        <v>0.1165371203318053</v>
+        <v>0.1170415016596086</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8589600269128828</v>
+        <v>0.8446440264643347</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1415506754459153</v>
+        <v>0.1425606754459153</v>
       </c>
       <c r="C62">
-        <v>4.109760321821927</v>
+        <v>3.575979060388001</v>
       </c>
       <c r="D62">
-        <v>19.51856032182193</v>
+        <v>19.334259060388</v>
       </c>
       <c r="E62">
-        <v>20.1208</v>
+        <v>20.47028</v>
       </c>
       <c r="F62">
-        <v>20.9688</v>
+        <v>21.31828</v>
       </c>
       <c r="G62">
         <v>5.56</v>
@@ -6359,37 +6359,37 @@
         <v>2.6</v>
       </c>
       <c r="M62">
-        <v>3.07821984</v>
+        <v>3.129523504000001</v>
       </c>
       <c r="N62">
-        <v>-0.47821984</v>
+        <v>-0.5295235040000006</v>
       </c>
       <c r="O62">
-        <v>-0.1147727616</v>
+        <v>-0.1270856409600001</v>
       </c>
       <c r="P62">
-        <v>-0.3634470784</v>
+        <v>-0.4024378630400005</v>
       </c>
       <c r="Q62">
-        <v>-0.02344707839999993</v>
+        <v>-0.06243786304000043</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1783144361253754</v>
+        <v>0.1817122421798722</v>
       </c>
       <c r="T62">
-        <v>2.234383766176256</v>
+        <v>2.291675657616674</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2027145663514403</v>
+        <v>0.1993913767391216</v>
       </c>
       <c r="W62">
-        <v>0.1170415016596086</v>
+        <v>0.117529345894697</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8446440264643347</v>
+        <v>0.8307974030796733</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1425606754459153</v>
+        <v>0.1435706754459153</v>
       </c>
       <c r="C63">
-        <v>3.575979060388001</v>
+        <v>3.045645719939834</v>
       </c>
       <c r="D63">
-        <v>19.334259060388</v>
+        <v>19.15340571993984</v>
       </c>
       <c r="E63">
-        <v>20.47028</v>
+        <v>20.81976</v>
       </c>
       <c r="F63">
-        <v>21.31828</v>
+        <v>21.66776</v>
       </c>
       <c r="G63">
         <v>5.56</v>
@@ -6441,37 +6441,37 @@
         <v>2.6</v>
       </c>
       <c r="M63">
-        <v>3.129523504000001</v>
+        <v>3.180827168</v>
       </c>
       <c r="N63">
-        <v>-0.5295235040000006</v>
+        <v>-0.5808271680000003</v>
       </c>
       <c r="O63">
-        <v>-0.1270856409600001</v>
+        <v>-0.1393985203200001</v>
       </c>
       <c r="P63">
-        <v>-0.4024378630400005</v>
+        <v>-0.4414286476800002</v>
       </c>
       <c r="Q63">
-        <v>-0.06243786304000043</v>
+        <v>-0.1014286476800002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1817122421798722</v>
+        <v>0.1852888801319741</v>
       </c>
       <c r="T63">
-        <v>2.291675657616674</v>
+        <v>2.35198291176448</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1993913767391216</v>
+        <v>0.1961753867917164</v>
       </c>
       <c r="W63">
-        <v>0.117529345894697</v>
+        <v>0.118001453218976</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8307974030796733</v>
+        <v>0.8173974449654851</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1435706754459153</v>
+        <v>0.1445806754459153</v>
       </c>
       <c r="C64">
-        <v>3.045645719939834</v>
+        <v>2.518664441225102</v>
       </c>
       <c r="D64">
-        <v>19.15340571993984</v>
+        <v>18.9759044412251</v>
       </c>
       <c r="E64">
-        <v>20.81976</v>
+        <v>21.16924</v>
       </c>
       <c r="F64">
-        <v>21.66776</v>
+        <v>22.01724</v>
       </c>
       <c r="G64">
         <v>5.56</v>
@@ -6523,37 +6523,37 @@
         <v>2.6</v>
       </c>
       <c r="M64">
-        <v>3.180827168</v>
+        <v>3.232130832000001</v>
       </c>
       <c r="N64">
-        <v>-0.5808271680000003</v>
+        <v>-0.6321308320000005</v>
       </c>
       <c r="O64">
-        <v>-0.1393985203200001</v>
+        <v>-0.1517113996800001</v>
       </c>
       <c r="P64">
-        <v>-0.4414286476800002</v>
+        <v>-0.4804194323200004</v>
       </c>
       <c r="Q64">
-        <v>-0.1014286476800002</v>
+        <v>-0.1404194323200004</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1852888801319741</v>
+        <v>0.1890588498652707</v>
       </c>
       <c r="T64">
-        <v>2.35198291176448</v>
+        <v>2.415550017487845</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1961753867917164</v>
+        <v>0.1930614917632764</v>
       </c>
       <c r="W64">
-        <v>0.118001453218976</v>
+        <v>0.118458573009151</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8173974449654851</v>
+        <v>0.8044228823469852</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1445806754459153</v>
+        <v>0.1821245126255065</v>
       </c>
       <c r="C65">
-        <v>2.518664441225102</v>
+        <v>-2.692857025615154</v>
       </c>
       <c r="D65">
-        <v>18.9759044412251</v>
+        <v>14.11386297438485</v>
       </c>
       <c r="E65">
-        <v>21.16924</v>
+        <v>21.51872</v>
       </c>
       <c r="F65">
-        <v>22.01724</v>
+        <v>22.36672</v>
       </c>
       <c r="G65">
         <v>5.56</v>
@@ -6605,45 +6605,45 @@
         <v>2.6</v>
       </c>
       <c r="M65">
-        <v>3.232130832000001</v>
+        <v>4.491237376</v>
       </c>
       <c r="N65">
-        <v>-0.6321308320000005</v>
+        <v>-1.891237376</v>
       </c>
       <c r="O65">
-        <v>-0.1517113996800001</v>
+        <v>-0.45389697024</v>
       </c>
       <c r="P65">
-        <v>-0.4804194323200004</v>
+        <v>-1.43734040576</v>
       </c>
       <c r="Q65">
-        <v>-0.1404194323200004</v>
+        <v>-1.09734040576</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1890588498652707</v>
+        <v>0.1985211434159482</v>
       </c>
       <c r="T65">
-        <v>2.415550017487845</v>
+        <v>2.575097880487653</v>
       </c>
       <c r="U65">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1930614917632764</v>
+        <v>0.1389372121220965</v>
       </c>
       <c r="W65">
-        <v>0.118458573009151</v>
+        <v>0.172901407805883</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8044228823469852</v>
+        <v>0.5789050505087354</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1821245126255065</v>
+        <v>0.1836745126255065</v>
       </c>
       <c r="C66">
-        <v>-2.692857025615154</v>
+        <v>-3.190072643289582</v>
       </c>
       <c r="D66">
-        <v>14.11386297438485</v>
+        <v>13.96612735671042</v>
       </c>
       <c r="E66">
-        <v>21.51872</v>
+        <v>21.8682</v>
       </c>
       <c r="F66">
-        <v>22.36672</v>
+        <v>22.7162</v>
       </c>
       <c r="G66">
         <v>5.56</v>
@@ -6687,37 +6687,37 @@
         <v>2.6</v>
       </c>
       <c r="M66">
-        <v>4.491237376</v>
+        <v>4.56141296</v>
       </c>
       <c r="N66">
-        <v>-1.891237376</v>
+        <v>-1.96141296</v>
       </c>
       <c r="O66">
-        <v>-0.45389697024</v>
+        <v>-0.4707391104</v>
       </c>
       <c r="P66">
-        <v>-1.43734040576</v>
+        <v>-1.4906738496</v>
       </c>
       <c r="Q66">
-        <v>-1.09734040576</v>
+        <v>-1.1506738496</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1985211434159482</v>
+        <v>0.2028846046564039</v>
       </c>
       <c r="T66">
-        <v>2.575097880487653</v>
+        <v>2.648672105644443</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1389372121220965</v>
+        <v>0.1367997165509873</v>
       </c>
       <c r="W66">
-        <v>0.172901407805883</v>
+        <v>0.1733306169165618</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5789050505087354</v>
+        <v>0.5699988189624471</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1836745126255065</v>
+        <v>0.1852245126255065</v>
       </c>
       <c r="C67">
-        <v>-3.190072643289582</v>
+        <v>-3.684227480282406</v>
       </c>
       <c r="D67">
-        <v>13.96612735671042</v>
+        <v>13.8214525197176</v>
       </c>
       <c r="E67">
-        <v>21.8682</v>
+        <v>22.21768</v>
       </c>
       <c r="F67">
-        <v>22.7162</v>
+        <v>23.06568</v>
       </c>
       <c r="G67">
         <v>5.56</v>
@@ -6769,37 +6769,37 @@
         <v>2.6</v>
       </c>
       <c r="M67">
-        <v>4.56141296</v>
+        <v>4.631588544</v>
       </c>
       <c r="N67">
-        <v>-1.96141296</v>
+        <v>-2.031588544</v>
       </c>
       <c r="O67">
-        <v>-0.4707391104</v>
+        <v>-0.4875812505600001</v>
       </c>
       <c r="P67">
-        <v>-1.4906738496</v>
+        <v>-1.54400729344</v>
       </c>
       <c r="Q67">
-        <v>-1.1506738496</v>
+        <v>-1.20400729344</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2028846046564039</v>
+        <v>0.2075047400874746</v>
       </c>
       <c r="T67">
-        <v>2.648672105644443</v>
+        <v>2.726574226398692</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1367997165509873</v>
+        <v>0.134726993572942</v>
       </c>
       <c r="W67">
-        <v>0.1733306169165618</v>
+        <v>0.1737468196905533</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5699988189624471</v>
+        <v>0.5613624732205917</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1852245126255065</v>
+        <v>0.1867745126255065</v>
       </c>
       <c r="C68">
-        <v>-3.684227480282406</v>
+        <v>-4.17541568105263</v>
       </c>
       <c r="D68">
-        <v>13.8214525197176</v>
+        <v>13.67974431894737</v>
       </c>
       <c r="E68">
-        <v>22.21768</v>
+        <v>22.56716</v>
       </c>
       <c r="F68">
-        <v>23.06568</v>
+        <v>23.41516</v>
       </c>
       <c r="G68">
         <v>5.56</v>
@@ -6851,37 +6851,37 @@
         <v>2.6</v>
       </c>
       <c r="M68">
-        <v>4.631588544</v>
+        <v>4.701764128</v>
       </c>
       <c r="N68">
-        <v>-2.031588544</v>
+        <v>-2.101764128</v>
       </c>
       <c r="O68">
-        <v>-0.4875812505600001</v>
+        <v>-0.5044233907199999</v>
       </c>
       <c r="P68">
-        <v>-1.54400729344</v>
+        <v>-1.59734073728</v>
       </c>
       <c r="Q68">
-        <v>-1.20400729344</v>
+        <v>-1.25734073728</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2075047400874746</v>
+        <v>0.212404883726489</v>
       </c>
       <c r="T68">
-        <v>2.726574226398692</v>
+        <v>2.809197687804713</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.134726993572942</v>
+        <v>0.1327161429225996</v>
       </c>
       <c r="W68">
-        <v>0.1737468196905533</v>
+        <v>0.174150598501142</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5613624732205917</v>
+        <v>0.5529839288441651</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1867745126255065</v>
+        <v>0.1883245126255065</v>
       </c>
       <c r="C69">
-        <v>-4.17541568105263</v>
+        <v>-4.66372756827645</v>
       </c>
       <c r="D69">
-        <v>13.67974431894737</v>
+        <v>13.54091243172356</v>
       </c>
       <c r="E69">
-        <v>22.56716</v>
+        <v>22.91664</v>
       </c>
       <c r="F69">
-        <v>23.41516</v>
+        <v>23.76464</v>
       </c>
       <c r="G69">
         <v>5.56</v>
@@ -6933,37 +6933,37 @@
         <v>2.6</v>
       </c>
       <c r="M69">
-        <v>4.701764128</v>
+        <v>4.771939712000001</v>
       </c>
       <c r="N69">
-        <v>-2.101764128</v>
+        <v>-2.171939712000001</v>
       </c>
       <c r="O69">
-        <v>-0.5044233907199999</v>
+        <v>-0.5212655308800002</v>
       </c>
       <c r="P69">
-        <v>-1.59734073728</v>
+        <v>-1.650674181120001</v>
       </c>
       <c r="Q69">
-        <v>-1.25734073728</v>
+        <v>-1.310674181120001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.212404883726489</v>
+        <v>0.2176112863429418</v>
       </c>
       <c r="T69">
-        <v>2.809197687804713</v>
+        <v>2.89698511554861</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1327161429225996</v>
+        <v>0.1307644349384437</v>
       </c>
       <c r="W69">
-        <v>0.174150598501142</v>
+        <v>0.1745425014643605</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5529839288441651</v>
+        <v>0.5448518122435155</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1883245126255065</v>
+        <v>0.1898745126255065</v>
       </c>
       <c r="C70">
-        <v>-4.66372756827645</v>
+        <v>-5.14924983482986</v>
       </c>
       <c r="D70">
-        <v>13.54091243172356</v>
+        <v>13.40487016517014</v>
       </c>
       <c r="E70">
-        <v>22.91664</v>
+        <v>23.26612</v>
       </c>
       <c r="F70">
-        <v>23.76464</v>
+        <v>24.11412</v>
       </c>
       <c r="G70">
         <v>5.56</v>
@@ -7015,37 +7015,37 @@
         <v>2.6</v>
       </c>
       <c r="M70">
-        <v>4.771939712000001</v>
+        <v>4.842115296000001</v>
       </c>
       <c r="N70">
-        <v>-2.171939712000001</v>
+        <v>-2.242115296000001</v>
       </c>
       <c r="O70">
-        <v>-0.5212655308800002</v>
+        <v>-0.5381076710400002</v>
       </c>
       <c r="P70">
-        <v>-1.650674181120001</v>
+        <v>-1.704007624960001</v>
       </c>
       <c r="Q70">
-        <v>-1.310674181120001</v>
+        <v>-1.364007624960001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2176112863429418</v>
+        <v>0.2231535859023915</v>
       </c>
       <c r="T70">
-        <v>2.89698511554861</v>
+        <v>2.990436248308243</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1307644349384437</v>
+        <v>0.1288692982002054</v>
       </c>
       <c r="W70">
-        <v>0.1745425014643605</v>
+        <v>0.1749230449213988</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5448518122435155</v>
+        <v>0.5369554091675226</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1898745126255065</v>
+        <v>0.1914245126255065</v>
       </c>
       <c r="C71">
-        <v>-5.14924983482986</v>
+        <v>-5.632065724313627</v>
       </c>
       <c r="D71">
-        <v>13.40487016517014</v>
+        <v>13.27153427568638</v>
       </c>
       <c r="E71">
-        <v>23.26612</v>
+        <v>23.6156</v>
       </c>
       <c r="F71">
-        <v>24.11412</v>
+        <v>24.4636</v>
       </c>
       <c r="G71">
         <v>5.56</v>
@@ -7097,37 +7097,37 @@
         <v>2.6</v>
       </c>
       <c r="M71">
-        <v>4.842115296000001</v>
+        <v>4.91229088</v>
       </c>
       <c r="N71">
-        <v>-2.242115296000001</v>
+        <v>-2.31229088</v>
       </c>
       <c r="O71">
-        <v>-0.5381076710400002</v>
+        <v>-0.5549498112000001</v>
       </c>
       <c r="P71">
-        <v>-1.704007624960001</v>
+        <v>-1.7573410688</v>
       </c>
       <c r="Q71">
-        <v>-1.364007624960001</v>
+        <v>-1.4173410688</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2231535859023915</v>
+        <v>0.2290653720991379</v>
       </c>
       <c r="T71">
-        <v>2.990436248308243</v>
+        <v>3.090117456585184</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1288692982002054</v>
+        <v>0.1270283082259168</v>
       </c>
       <c r="W71">
-        <v>0.1749230449213988</v>
+        <v>0.1752927157082359</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5369554091675226</v>
+        <v>0.5292846176079866</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1914245126255065</v>
+        <v>0.1929745126255065</v>
       </c>
       <c r="C72">
-        <v>-5.632065724313627</v>
+        <v>-6.11225520091039</v>
       </c>
       <c r="D72">
-        <v>13.27153427568638</v>
+        <v>13.14082479908961</v>
       </c>
       <c r="E72">
-        <v>23.6156</v>
+        <v>23.96508</v>
       </c>
       <c r="F72">
-        <v>24.4636</v>
+        <v>24.81308</v>
       </c>
       <c r="G72">
         <v>5.56</v>
@@ -7179,37 +7179,37 @@
         <v>2.6</v>
       </c>
       <c r="M72">
-        <v>4.91229088</v>
+        <v>4.982466464000001</v>
       </c>
       <c r="N72">
-        <v>-2.31229088</v>
+        <v>-2.382466464000001</v>
       </c>
       <c r="O72">
-        <v>-0.5549498112000001</v>
+        <v>-0.5717919513600002</v>
       </c>
       <c r="P72">
-        <v>-1.7573410688</v>
+        <v>-1.81067451264</v>
       </c>
       <c r="Q72">
-        <v>-1.4173410688</v>
+        <v>-1.47067451264</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2290653720991379</v>
+        <v>0.2353848676887634</v>
       </c>
       <c r="T72">
-        <v>3.090117456585184</v>
+        <v>3.196673230950191</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1270283082259168</v>
+        <v>0.1252391771241433</v>
       </c>
       <c r="W72">
-        <v>0.1752927157082359</v>
+        <v>0.175651973233472</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5292846176079866</v>
+        <v>0.5218299046839304</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1929745126255065</v>
+        <v>0.1945245126255065</v>
       </c>
       <c r="C73">
-        <v>-6.112255200910386</v>
+        <v>-6.589895109302304</v>
       </c>
       <c r="D73">
-        <v>13.14082479908961</v>
+        <v>13.0126648906977</v>
       </c>
       <c r="E73">
-        <v>23.96508</v>
+        <v>24.31456</v>
       </c>
       <c r="F73">
-        <v>24.81308</v>
+        <v>25.16256</v>
       </c>
       <c r="G73">
         <v>5.56</v>
@@ -7261,37 +7261,37 @@
         <v>2.6</v>
       </c>
       <c r="M73">
-        <v>4.982466464</v>
+        <v>5.052642048</v>
       </c>
       <c r="N73">
-        <v>-2.382466464</v>
+        <v>-2.452642048</v>
       </c>
       <c r="O73">
-        <v>-0.5717919513599999</v>
+        <v>-0.58863409152</v>
       </c>
       <c r="P73">
-        <v>-1.81067451264</v>
+        <v>-1.86400795648</v>
       </c>
       <c r="Q73">
-        <v>-1.47067451264</v>
+        <v>-1.52400795648</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2353848676887633</v>
+        <v>0.2421557558205048</v>
       </c>
       <c r="T73">
-        <v>3.19667323095019</v>
+        <v>3.310840132055553</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1252391771241433</v>
+        <v>0.1234997441085302</v>
       </c>
       <c r="W73">
-        <v>0.175651973233472</v>
+        <v>0.1760012513830072</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5218299046839305</v>
+        <v>0.5145822671188759</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1945245126255065</v>
+        <v>0.1960745126255065</v>
       </c>
       <c r="C74">
-        <v>-6.589895109302304</v>
+        <v>-7.065059325321201</v>
       </c>
       <c r="D74">
-        <v>13.0126648906977</v>
+        <v>12.8869806746788</v>
       </c>
       <c r="E74">
-        <v>24.31456</v>
+        <v>24.66404</v>
       </c>
       <c r="F74">
-        <v>25.16256</v>
+        <v>25.51204</v>
       </c>
       <c r="G74">
         <v>5.56</v>
@@ -7343,37 +7343,37 @@
         <v>2.6</v>
       </c>
       <c r="M74">
-        <v>5.052642048</v>
+        <v>5.122817632</v>
       </c>
       <c r="N74">
-        <v>-2.452642048</v>
+        <v>-2.522817632</v>
       </c>
       <c r="O74">
-        <v>-0.58863409152</v>
+        <v>-0.60547623168</v>
       </c>
       <c r="P74">
-        <v>-1.86400795648</v>
+        <v>-1.91734140032</v>
       </c>
       <c r="Q74">
-        <v>-1.52400795648</v>
+        <v>-1.57734140032</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2421557558205048</v>
+        <v>0.2494281912212643</v>
       </c>
       <c r="T74">
-        <v>3.310840132055553</v>
+        <v>3.433463840650203</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1234997441085302</v>
+        <v>0.121807966791975</v>
       </c>
       <c r="W74">
-        <v>0.1760012513830072</v>
+        <v>0.1763409602681714</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5145822671188759</v>
+        <v>0.5075331949665625</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1960745126255065</v>
+        <v>0.1976245126255065</v>
       </c>
       <c r="C75">
-        <v>-7.065059325321201</v>
+        <v>-7.537818897951805</v>
       </c>
       <c r="D75">
-        <v>12.8869806746788</v>
+        <v>12.76370110204819</v>
       </c>
       <c r="E75">
-        <v>24.66404</v>
+        <v>25.01352</v>
       </c>
       <c r="F75">
-        <v>25.51204</v>
+        <v>25.86152</v>
       </c>
       <c r="G75">
         <v>5.56</v>
@@ -7425,37 +7425,37 @@
         <v>2.6</v>
       </c>
       <c r="M75">
-        <v>5.122817632</v>
+        <v>5.192993216</v>
       </c>
       <c r="N75">
-        <v>-2.522817632</v>
+        <v>-2.592993216</v>
       </c>
       <c r="O75">
-        <v>-0.60547623168</v>
+        <v>-0.6223183718399998</v>
       </c>
       <c r="P75">
-        <v>-1.91734140032</v>
+        <v>-1.97067484416</v>
       </c>
       <c r="Q75">
-        <v>-1.57734140032</v>
+        <v>-1.63067484416</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2494281912212643</v>
+        <v>0.2572600447297744</v>
       </c>
       <c r="T75">
-        <v>3.433463840650203</v>
+        <v>3.565520142213673</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.121807966791975</v>
+        <v>0.120161913186678</v>
       </c>
       <c r="W75">
-        <v>0.1763409602681714</v>
+        <v>0.1766714878321151</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5075331949665625</v>
+        <v>0.5006746382778252</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1976245126255065</v>
+        <v>0.2262209797687807</v>
       </c>
       <c r="C76">
-        <v>-7.537818897951805</v>
+        <v>-9.802035037074081</v>
       </c>
       <c r="D76">
-        <v>12.76370110204819</v>
+        <v>10.84896496292592</v>
       </c>
       <c r="E76">
-        <v>25.01352</v>
+        <v>25.363</v>
       </c>
       <c r="F76">
-        <v>25.86152</v>
+        <v>26.211</v>
       </c>
       <c r="G76">
         <v>5.56</v>
@@ -7507,45 +7507,45 @@
         <v>2.6</v>
       </c>
       <c r="M76">
-        <v>5.192993216</v>
+        <v>6.1805538</v>
       </c>
       <c r="N76">
-        <v>-2.592993216</v>
+        <v>-3.5805538</v>
       </c>
       <c r="O76">
-        <v>-0.6223183718399998</v>
+        <v>-0.8593329119999999</v>
       </c>
       <c r="P76">
-        <v>-1.97067484416</v>
+        <v>-2.721220888</v>
       </c>
       <c r="Q76">
-        <v>-1.63067484416</v>
+        <v>-2.381220888000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2572600447297744</v>
+        <v>0.2689043150920624</v>
       </c>
       <c r="T76">
-        <v>3.565520142213673</v>
+        <v>3.761859268932271</v>
       </c>
       <c r="U76">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.120161913186678</v>
+        <v>0.1009618264305053</v>
       </c>
       <c r="W76">
-        <v>0.1766714878321151</v>
+        <v>0.2119932013276868</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.5006746382778252</v>
+        <v>0.4206742767937721</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2262209797687807</v>
+        <v>0.2281209797687808</v>
       </c>
       <c r="C77">
-        <v>-9.802035037074081</v>
+        <v>-10.25858177238169</v>
       </c>
       <c r="D77">
-        <v>10.84896496292592</v>
+        <v>10.74189822761831</v>
       </c>
       <c r="E77">
-        <v>25.363</v>
+        <v>25.71248</v>
       </c>
       <c r="F77">
-        <v>26.211</v>
+        <v>26.56048</v>
       </c>
       <c r="G77">
         <v>5.56</v>
@@ -7589,37 +7589,37 @@
         <v>2.6</v>
       </c>
       <c r="M77">
-        <v>6.1805538</v>
+        <v>6.262961184000001</v>
       </c>
       <c r="N77">
-        <v>-3.5805538</v>
+        <v>-3.662961184000001</v>
       </c>
       <c r="O77">
-        <v>-0.8593329119999999</v>
+        <v>-0.8791106841600002</v>
       </c>
       <c r="P77">
-        <v>-2.721220888</v>
+        <v>-2.783850499840001</v>
       </c>
       <c r="Q77">
-        <v>-2.381220888000001</v>
+        <v>-2.443850499840001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2689043150920624</v>
+        <v>0.2782003282208984</v>
       </c>
       <c r="T77">
-        <v>3.761859268932271</v>
+        <v>3.918603405137782</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1009618264305053</v>
+        <v>0.09963338134589338</v>
       </c>
       <c r="W77">
-        <v>0.2119932013276868</v>
+        <v>0.2123064486786383</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4206742767937721</v>
+        <v>0.4151390889412224</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2281209797687808</v>
+        <v>0.2300209797687807</v>
       </c>
       <c r="C78">
-        <v>-10.25858177238169</v>
+        <v>-10.71303590954334</v>
       </c>
       <c r="D78">
-        <v>10.74189822761831</v>
+        <v>10.63692409045667</v>
       </c>
       <c r="E78">
-        <v>25.71248</v>
+        <v>26.06196</v>
       </c>
       <c r="F78">
-        <v>26.56048</v>
+        <v>26.90996</v>
       </c>
       <c r="G78">
         <v>5.56</v>
@@ -7671,37 +7671,37 @@
         <v>2.6</v>
       </c>
       <c r="M78">
-        <v>6.262961184000001</v>
+        <v>6.345368568</v>
       </c>
       <c r="N78">
-        <v>-3.662961184000001</v>
+        <v>-3.745368568</v>
       </c>
       <c r="O78">
-        <v>-0.8791106841600002</v>
+        <v>-0.89888845632</v>
       </c>
       <c r="P78">
-        <v>-2.783850499840001</v>
+        <v>-2.84648011168</v>
       </c>
       <c r="Q78">
-        <v>-2.443850499840001</v>
+        <v>-2.506480111680001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2782003282208984</v>
+        <v>0.2883046903174591</v>
       </c>
       <c r="T78">
-        <v>3.918603405137782</v>
+        <v>4.088977466230729</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09963338134589338</v>
+        <v>0.09833944132841424</v>
       </c>
       <c r="W78">
-        <v>0.2123064486786383</v>
+        <v>0.2126115597347599</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4151390889412224</v>
+        <v>0.409747672201726</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2300209797687807</v>
+        <v>0.2319209797687807</v>
       </c>
       <c r="C79">
-        <v>-10.71303590954334</v>
+        <v>-11.16545820395764</v>
       </c>
       <c r="D79">
-        <v>10.63692409045667</v>
+        <v>10.53398179604236</v>
       </c>
       <c r="E79">
-        <v>26.06196</v>
+        <v>26.41144</v>
       </c>
       <c r="F79">
-        <v>26.90996</v>
+        <v>27.25944</v>
       </c>
       <c r="G79">
         <v>5.56</v>
@@ -7753,37 +7753,37 @@
         <v>2.6</v>
       </c>
       <c r="M79">
-        <v>6.345368568</v>
+        <v>6.427775952</v>
       </c>
       <c r="N79">
-        <v>-3.745368568</v>
+        <v>-3.827775952</v>
       </c>
       <c r="O79">
-        <v>-0.89888845632</v>
+        <v>-0.91866622848</v>
       </c>
       <c r="P79">
-        <v>-2.84648011168</v>
+        <v>-2.90910972352</v>
       </c>
       <c r="Q79">
-        <v>-2.506480111680001</v>
+        <v>-2.56910972352</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2883046903174591</v>
+        <v>0.2993276307864346</v>
       </c>
       <c r="T79">
-        <v>4.088977466230729</v>
+        <v>4.274840078332126</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09833944132841424</v>
+        <v>0.09707867926010125</v>
       </c>
       <c r="W79">
-        <v>0.2126115597347599</v>
+        <v>0.2129088474304681</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.409747672201726</v>
+        <v>0.4044944969170886</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2319209797687807</v>
+        <v>0.2338209797687807</v>
       </c>
       <c r="C80">
-        <v>-11.16545820395764</v>
+        <v>-11.61590708164598</v>
       </c>
       <c r="D80">
-        <v>10.53398179604236</v>
+        <v>10.43301291835402</v>
       </c>
       <c r="E80">
-        <v>26.41144</v>
+        <v>26.76092</v>
       </c>
       <c r="F80">
-        <v>27.25944</v>
+        <v>27.60892</v>
       </c>
       <c r="G80">
         <v>5.56</v>
@@ -7835,37 +7835,37 @@
         <v>2.6</v>
       </c>
       <c r="M80">
-        <v>6.427775952</v>
+        <v>6.510183336000001</v>
       </c>
       <c r="N80">
-        <v>-3.827775952</v>
+        <v>-3.910183336000001</v>
       </c>
       <c r="O80">
-        <v>-0.91866622848</v>
+        <v>-0.9384440006400001</v>
       </c>
       <c r="P80">
-        <v>-2.90910972352</v>
+        <v>-2.971739335360001</v>
       </c>
       <c r="Q80">
-        <v>-2.56910972352</v>
+        <v>-2.631739335360001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2993276307864346</v>
+        <v>0.3114003751095982</v>
       </c>
       <c r="T80">
-        <v>4.274840078332126</v>
+        <v>4.478403891586037</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09707867926010125</v>
+        <v>0.09584983521883414</v>
       </c>
       <c r="W80">
-        <v>0.2129088474304681</v>
+        <v>0.2131986088553989</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4044944969170886</v>
+        <v>0.399374313411809</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2338209797687807</v>
+        <v>0.2357209797687808</v>
       </c>
       <c r="C81">
-        <v>-11.61590708164598</v>
+        <v>-12.06443874982871</v>
       </c>
       <c r="D81">
-        <v>10.43301291835402</v>
+        <v>10.33396125017129</v>
       </c>
       <c r="E81">
-        <v>26.76092</v>
+        <v>27.1104</v>
       </c>
       <c r="F81">
-        <v>27.60892</v>
+        <v>27.9584</v>
       </c>
       <c r="G81">
         <v>5.56</v>
@@ -7917,37 +7917,37 @@
         <v>2.6</v>
       </c>
       <c r="M81">
-        <v>6.510183336000001</v>
+        <v>6.59259072</v>
       </c>
       <c r="N81">
-        <v>-3.910183336000001</v>
+        <v>-3.99259072</v>
       </c>
       <c r="O81">
-        <v>-0.9384440006400001</v>
+        <v>-0.9582217728000001</v>
       </c>
       <c r="P81">
-        <v>-2.971739335360001</v>
+        <v>-3.0343689472</v>
       </c>
       <c r="Q81">
-        <v>-2.631739335360001</v>
+        <v>-2.694368947200001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3114003751095982</v>
+        <v>0.3246803938650781</v>
       </c>
       <c r="T81">
-        <v>4.478403891586037</v>
+        <v>4.702324086165339</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09584983521883414</v>
+        <v>0.09465171227859871</v>
       </c>
       <c r="W81">
-        <v>0.2131986088553989</v>
+        <v>0.2134811262447064</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.399374313411809</v>
+        <v>0.3943821344941614</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2357209797687808</v>
+        <v>0.2376209797687807</v>
       </c>
       <c r="C82">
-        <v>-12.06443874982871</v>
+        <v>-12.5111073012618</v>
       </c>
       <c r="D82">
-        <v>10.33396125017129</v>
+        <v>10.2367726987382</v>
       </c>
       <c r="E82">
-        <v>27.1104</v>
+        <v>27.45988</v>
       </c>
       <c r="F82">
-        <v>27.9584</v>
+        <v>28.30788</v>
       </c>
       <c r="G82">
         <v>5.56</v>
@@ -7999,37 +7999,37 @@
         <v>2.6</v>
       </c>
       <c r="M82">
-        <v>6.59259072</v>
+        <v>6.674998104</v>
       </c>
       <c r="N82">
-        <v>-3.99259072</v>
+        <v>-4.074998104000001</v>
       </c>
       <c r="O82">
-        <v>-0.9582217728000001</v>
+        <v>-0.9779995449600001</v>
       </c>
       <c r="P82">
-        <v>-3.0343689472</v>
+        <v>-3.09699855904</v>
       </c>
       <c r="Q82">
-        <v>-2.694368947200001</v>
+        <v>-2.75699855904</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3246803938650781</v>
+        <v>0.3393583093316611</v>
       </c>
       <c r="T82">
-        <v>4.702324086165339</v>
+        <v>4.949814827542461</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09465171227859871</v>
+        <v>0.09348317262083825</v>
       </c>
       <c r="W82">
-        <v>0.2134811262447064</v>
+        <v>0.2137566678960063</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3943821344941614</v>
+        <v>0.3895132192534926</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2376209797687807</v>
+        <v>0.2395209797687808</v>
       </c>
       <c r="C83">
-        <v>-12.5111073012618</v>
+        <v>-12.95596481274066</v>
       </c>
       <c r="D83">
-        <v>10.2367726987382</v>
+        <v>10.14139518725935</v>
       </c>
       <c r="E83">
-        <v>27.45988</v>
+        <v>27.80936000000001</v>
       </c>
       <c r="F83">
-        <v>28.30788</v>
+        <v>28.65736</v>
       </c>
       <c r="G83">
         <v>5.56</v>
@@ -8081,37 +8081,37 @@
         <v>2.6</v>
       </c>
       <c r="M83">
-        <v>6.674998104</v>
+        <v>6.757405488000002</v>
       </c>
       <c r="N83">
-        <v>-4.074998104000001</v>
+        <v>-4.157405488000002</v>
       </c>
       <c r="O83">
-        <v>-0.9779995449600001</v>
+        <v>-0.9977773171200004</v>
       </c>
       <c r="P83">
-        <v>-3.09699855904</v>
+        <v>-3.159628170880001</v>
       </c>
       <c r="Q83">
-        <v>-2.75699855904</v>
+        <v>-2.819628170880002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3393583093316611</v>
+        <v>0.3556671042945312</v>
       </c>
       <c r="T83">
-        <v>4.949814827542461</v>
+        <v>5.224804540183711</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09348317262083825</v>
+        <v>0.09234313393034019</v>
       </c>
       <c r="W83">
-        <v>0.2137566678960063</v>
+        <v>0.2140254890192258</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3895132192534926</v>
+        <v>0.3847630580430841</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2395209797687808</v>
+        <v>0.2414209797687807</v>
       </c>
       <c r="C84">
-        <v>-12.95596481274066</v>
+        <v>-13.39906143814821</v>
       </c>
       <c r="D84">
-        <v>10.14139518725935</v>
+        <v>10.0477785618518</v>
       </c>
       <c r="E84">
-        <v>27.80936000000001</v>
+        <v>28.15884</v>
       </c>
       <c r="F84">
-        <v>28.65736</v>
+        <v>29.00684</v>
       </c>
       <c r="G84">
         <v>5.56</v>
@@ -8163,37 +8163,37 @@
         <v>2.6</v>
       </c>
       <c r="M84">
-        <v>6.757405488000002</v>
+        <v>6.839812872000001</v>
       </c>
       <c r="N84">
-        <v>-4.157405488000002</v>
+        <v>-4.239812872000002</v>
       </c>
       <c r="O84">
-        <v>-0.9977773171200004</v>
+        <v>-1.01755508928</v>
       </c>
       <c r="P84">
-        <v>-3.159628170880001</v>
+        <v>-3.222257782720002</v>
       </c>
       <c r="Q84">
-        <v>-2.819628170880002</v>
+        <v>-2.882257782720002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3556671042945312</v>
+        <v>0.3738945810177389</v>
       </c>
       <c r="T84">
-        <v>5.224804540183711</v>
+        <v>5.532145983723929</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09234313393034019</v>
+        <v>0.09123056605166141</v>
       </c>
       <c r="W84">
-        <v>0.2140254890192258</v>
+        <v>0.2142878325250182</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3847630580430841</v>
+        <v>0.3801273585485891</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2414209797687807</v>
+        <v>0.2433209797687808</v>
       </c>
       <c r="C85">
-        <v>-13.39906143814821</v>
+        <v>-13.84044549639646</v>
       </c>
       <c r="D85">
-        <v>10.0477785618518</v>
+        <v>9.955874503603548</v>
       </c>
       <c r="E85">
-        <v>28.15884</v>
+        <v>28.50832</v>
       </c>
       <c r="F85">
-        <v>29.00684</v>
+        <v>29.35632</v>
       </c>
       <c r="G85">
         <v>5.56</v>
@@ -8245,37 +8245,37 @@
         <v>2.6</v>
       </c>
       <c r="M85">
-        <v>6.839812872000001</v>
+        <v>6.922220256000001</v>
       </c>
       <c r="N85">
-        <v>-4.239812872000002</v>
+        <v>-4.322220256000001</v>
       </c>
       <c r="O85">
-        <v>-1.01755508928</v>
+        <v>-1.03733286144</v>
       </c>
       <c r="P85">
-        <v>-3.222257782720002</v>
+        <v>-3.284887394560001</v>
       </c>
       <c r="Q85">
-        <v>-2.882257782720002</v>
+        <v>-2.944887394560001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3738945810177389</v>
+        <v>0.3944004923313477</v>
       </c>
       <c r="T85">
-        <v>5.532145983723929</v>
+        <v>5.877905107706676</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09123056605166141</v>
+        <v>0.09014448788437972</v>
       </c>
       <c r="W85">
-        <v>0.2142878325250182</v>
+        <v>0.2145439297568633</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3801273585485891</v>
+        <v>0.3756020328515821</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2433209797687807</v>
+        <v>0.2452209797687808</v>
       </c>
       <c r="C86">
-        <v>-13.84044549639645</v>
+        <v>-14.28016355458554</v>
       </c>
       <c r="D86">
-        <v>9.95587450360355</v>
+        <v>9.865636445414463</v>
       </c>
       <c r="E86">
-        <v>28.50832</v>
+        <v>28.8578</v>
       </c>
       <c r="F86">
-        <v>29.35632</v>
+        <v>29.7058</v>
       </c>
       <c r="G86">
         <v>5.56</v>
@@ -8327,37 +8327,37 @@
         <v>2.6</v>
       </c>
       <c r="M86">
-        <v>6.922220256</v>
+        <v>7.004627640000001</v>
       </c>
       <c r="N86">
-        <v>-4.322220256</v>
+        <v>-4.404627640000001</v>
       </c>
       <c r="O86">
-        <v>-1.03733286144</v>
+        <v>-1.0571106336</v>
       </c>
       <c r="P86">
-        <v>-3.28488739456</v>
+        <v>-3.347517006400001</v>
       </c>
       <c r="Q86">
-        <v>-2.94488739456</v>
+        <v>-3.007517006400001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3944004923313474</v>
+        <v>0.4176405251534374</v>
       </c>
       <c r="T86">
-        <v>5.877905107706671</v>
+        <v>6.269765448220451</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09014448788437973</v>
+        <v>0.08908396449750468</v>
       </c>
       <c r="W86">
-        <v>0.2145439297568633</v>
+        <v>0.2147940011714884</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3756020328515823</v>
+        <v>0.3711831854062694</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2452209797687808</v>
+        <v>0.2471209797687807</v>
       </c>
       <c r="C87">
-        <v>-14.28016355458554</v>
+        <v>-14.71826050668097</v>
       </c>
       <c r="D87">
-        <v>9.865636445414463</v>
+        <v>9.777019493319035</v>
       </c>
       <c r="E87">
-        <v>28.8578</v>
+        <v>29.20728</v>
       </c>
       <c r="F87">
-        <v>29.7058</v>
+        <v>30.05528</v>
       </c>
       <c r="G87">
         <v>5.56</v>
@@ -8409,37 +8409,37 @@
         <v>2.6</v>
       </c>
       <c r="M87">
-        <v>7.004627640000001</v>
+        <v>7.087035024</v>
       </c>
       <c r="N87">
-        <v>-4.404627640000001</v>
+        <v>-4.487035024000001</v>
       </c>
       <c r="O87">
-        <v>-1.0571106336</v>
+        <v>-1.07688840576</v>
       </c>
       <c r="P87">
-        <v>-3.347517006400001</v>
+        <v>-3.410146618240001</v>
       </c>
       <c r="Q87">
-        <v>-3.007517006400001</v>
+        <v>-3.070146618240001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4176405251534374</v>
+        <v>0.4442005626643971</v>
       </c>
       <c r="T87">
-        <v>6.269765448220451</v>
+        <v>6.717605837379054</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08908396449750468</v>
+        <v>0.08804810444520811</v>
       </c>
       <c r="W87">
-        <v>0.2147940011714884</v>
+        <v>0.2150382569718199</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3711831854062694</v>
+        <v>0.3668671018550338</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2471209797687807</v>
+        <v>0.2490209797687808</v>
       </c>
       <c r="C88">
-        <v>-14.71826050668097</v>
+        <v>-15.15477964798837</v>
       </c>
       <c r="D88">
-        <v>9.777019493319035</v>
+        <v>9.689980352011634</v>
       </c>
       <c r="E88">
-        <v>29.20728</v>
+        <v>29.55676</v>
       </c>
       <c r="F88">
-        <v>30.05528</v>
+        <v>30.40476</v>
       </c>
       <c r="G88">
         <v>5.56</v>
@@ -8491,37 +8491,37 @@
         <v>2.6</v>
       </c>
       <c r="M88">
-        <v>7.087035024</v>
+        <v>7.169442408</v>
       </c>
       <c r="N88">
-        <v>-4.487035024000001</v>
+        <v>-4.569442408</v>
       </c>
       <c r="O88">
-        <v>-1.07688840576</v>
+        <v>-1.09666617792</v>
       </c>
       <c r="P88">
-        <v>-3.410146618240001</v>
+        <v>-3.47277623008</v>
       </c>
       <c r="Q88">
-        <v>-3.070146618240001</v>
+        <v>-3.132776230080001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4442005626643971</v>
+        <v>0.4748467597924277</v>
       </c>
       <c r="T88">
-        <v>6.717605837379054</v>
+        <v>7.234344747946674</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08804810444520811</v>
+        <v>0.08703605726767699</v>
       </c>
       <c r="W88">
-        <v>0.2150382569718199</v>
+        <v>0.2152768976962818</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3668671018550338</v>
+        <v>0.3626502386153208</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2490209797687808</v>
+        <v>0.2509209797687807</v>
       </c>
       <c r="C89">
-        <v>-15.15477964798837</v>
+        <v>-15.58976274568529</v>
       </c>
       <c r="D89">
-        <v>9.689980352011634</v>
+        <v>9.604477254314709</v>
       </c>
       <c r="E89">
-        <v>29.55676</v>
+        <v>29.90624</v>
       </c>
       <c r="F89">
-        <v>30.40476</v>
+        <v>30.75424</v>
       </c>
       <c r="G89">
         <v>5.56</v>
@@ -8573,37 +8573,37 @@
         <v>2.6</v>
       </c>
       <c r="M89">
-        <v>7.169442408</v>
+        <v>7.251849792</v>
       </c>
       <c r="N89">
-        <v>-4.569442408</v>
+        <v>-4.651849792</v>
       </c>
       <c r="O89">
-        <v>-1.09666617792</v>
+        <v>-1.11644395008</v>
       </c>
       <c r="P89">
-        <v>-3.47277623008</v>
+        <v>-3.53540584192</v>
       </c>
       <c r="Q89">
-        <v>-3.132776230080001</v>
+        <v>-3.19540584192</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4748467597924277</v>
+        <v>0.5106006564417966</v>
       </c>
       <c r="T89">
-        <v>7.234344747946674</v>
+        <v>7.837206810275564</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08703605726767699</v>
+        <v>0.08604701116236248</v>
       </c>
       <c r="W89">
-        <v>0.2152768976962818</v>
+        <v>0.2155101147679149</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3626502386153208</v>
+        <v>0.3585292131765103</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2509209797687807</v>
+        <v>0.2528209797687808</v>
       </c>
       <c r="C90">
-        <v>-15.58976274568529</v>
+        <v>-16.02325010565152</v>
       </c>
       <c r="D90">
-        <v>9.604477254314709</v>
+        <v>9.52046989434848</v>
       </c>
       <c r="E90">
-        <v>29.90624</v>
+        <v>30.25572</v>
       </c>
       <c r="F90">
-        <v>30.75424</v>
+        <v>31.10372</v>
       </c>
       <c r="G90">
         <v>5.56</v>
@@ -8655,37 +8655,37 @@
         <v>2.6</v>
       </c>
       <c r="M90">
-        <v>7.251849792</v>
+        <v>7.334257176</v>
       </c>
       <c r="N90">
-        <v>-4.651849792</v>
+        <v>-4.734257176</v>
       </c>
       <c r="O90">
-        <v>-1.11644395008</v>
+        <v>-1.13622172224</v>
       </c>
       <c r="P90">
-        <v>-3.53540584192</v>
+        <v>-3.59803545376</v>
       </c>
       <c r="Q90">
-        <v>-3.19540584192</v>
+        <v>-3.25803545376</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5106006564417966</v>
+        <v>0.5528552615728691</v>
       </c>
       <c r="T90">
-        <v>7.837206810275564</v>
+        <v>8.549680156664252</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08604701116236248</v>
+        <v>0.08508019081222357</v>
       </c>
       <c r="W90">
-        <v>0.2155101147679149</v>
+        <v>0.2157380910064777</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3585292131765103</v>
+        <v>0.3545007950509316</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2528209797687808</v>
+        <v>0.2547209797687807</v>
       </c>
       <c r="C91">
-        <v>-16.02325010565152</v>
+        <v>-16.45528063582249</v>
       </c>
       <c r="D91">
-        <v>9.52046989434848</v>
+        <v>9.43791936417751</v>
       </c>
       <c r="E91">
-        <v>30.25572</v>
+        <v>30.6052</v>
       </c>
       <c r="F91">
-        <v>31.10372</v>
+        <v>31.4532</v>
       </c>
       <c r="G91">
         <v>5.56</v>
@@ -8737,37 +8737,37 @@
         <v>2.6</v>
       </c>
       <c r="M91">
-        <v>7.334257176</v>
+        <v>7.416664560000001</v>
       </c>
       <c r="N91">
-        <v>-4.734257176</v>
+        <v>-4.816664560000001</v>
       </c>
       <c r="O91">
-        <v>-1.13622172224</v>
+        <v>-1.1559994944</v>
       </c>
       <c r="P91">
-        <v>-3.59803545376</v>
+        <v>-3.660665065600001</v>
       </c>
       <c r="Q91">
-        <v>-3.25803545376</v>
+        <v>-3.320665065600001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5528552615728691</v>
+        <v>0.6035607877301561</v>
       </c>
       <c r="T91">
-        <v>8.549680156664252</v>
+        <v>9.404648172330678</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08508019081222357</v>
+        <v>0.08413485535875441</v>
       </c>
       <c r="W91">
-        <v>0.2157380910064777</v>
+        <v>0.2159610011064057</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3545007950509316</v>
+        <v>0.3505618973281434</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2547209797687807</v>
+        <v>0.2566209797687807</v>
       </c>
       <c r="C92">
-        <v>-16.45528063582249</v>
+        <v>-16.88589190627511</v>
       </c>
       <c r="D92">
-        <v>9.43791936417751</v>
+        <v>9.356788093724891</v>
       </c>
       <c r="E92">
-        <v>30.6052</v>
+        <v>30.95468</v>
       </c>
       <c r="F92">
-        <v>31.4532</v>
+        <v>31.80268</v>
       </c>
       <c r="G92">
         <v>5.56</v>
@@ -8819,37 +8819,37 @@
         <v>2.6</v>
       </c>
       <c r="M92">
-        <v>7.416664560000001</v>
+        <v>7.499071944000001</v>
       </c>
       <c r="N92">
-        <v>-4.816664560000001</v>
+        <v>-4.899071944000001</v>
       </c>
       <c r="O92">
-        <v>-1.1559994944</v>
+        <v>-1.17577726656</v>
       </c>
       <c r="P92">
-        <v>-3.660665065600001</v>
+        <v>-3.723294677440001</v>
       </c>
       <c r="Q92">
-        <v>-3.320665065600001</v>
+        <v>-3.383294677440001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6035607877301561</v>
+        <v>0.6655342085890624</v>
       </c>
       <c r="T92">
-        <v>9.404648172330678</v>
+        <v>10.44960908036742</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08413485535875441</v>
+        <v>0.08321029650865822</v>
       </c>
       <c r="W92">
-        <v>0.2159610011064057</v>
+        <v>0.2161790120832584</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3505618973281434</v>
+        <v>0.3467095687860758</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2566209797687807</v>
+        <v>0.2585209797687807</v>
       </c>
       <c r="C93">
-        <v>-16.88589190627511</v>
+        <v>-17.31512020624088</v>
       </c>
       <c r="D93">
-        <v>9.356788093724891</v>
+        <v>9.277039793759121</v>
       </c>
       <c r="E93">
-        <v>30.95468</v>
+        <v>31.30416</v>
       </c>
       <c r="F93">
-        <v>31.80268</v>
+        <v>32.15216</v>
       </c>
       <c r="G93">
         <v>5.56</v>
@@ -8901,37 +8901,37 @@
         <v>2.6</v>
       </c>
       <c r="M93">
-        <v>7.499071944000001</v>
+        <v>7.581479328000001</v>
       </c>
       <c r="N93">
-        <v>-4.899071944000001</v>
+        <v>-4.981479328000001</v>
       </c>
       <c r="O93">
-        <v>-1.17577726656</v>
+        <v>-1.19555503872</v>
       </c>
       <c r="P93">
-        <v>-3.723294677440001</v>
+        <v>-3.78592428928</v>
       </c>
       <c r="Q93">
-        <v>-3.383294677440001</v>
+        <v>-3.445924289280001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6655342085890624</v>
+        <v>0.7430009846626954</v>
       </c>
       <c r="T93">
-        <v>10.44960908036742</v>
+        <v>11.75581021541335</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08321029650865822</v>
+        <v>0.08230583676399887</v>
       </c>
       <c r="W93">
-        <v>0.2161790120832584</v>
+        <v>0.2163922836910491</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3467095687860758</v>
+        <v>0.342940986516662</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2585209797687807</v>
+        <v>0.2604209797687808</v>
       </c>
       <c r="C94">
-        <v>-17.31512020624088</v>
+        <v>-17.74300059822811</v>
       </c>
       <c r="D94">
-        <v>9.277039793759121</v>
+        <v>9.19863940177189</v>
       </c>
       <c r="E94">
-        <v>31.30416</v>
+        <v>31.65364</v>
       </c>
       <c r="F94">
-        <v>32.15216</v>
+        <v>32.50164</v>
       </c>
       <c r="G94">
         <v>5.56</v>
@@ -8983,37 +8983,37 @@
         <v>2.6</v>
       </c>
       <c r="M94">
-        <v>7.581479328000001</v>
+        <v>7.663886712000001</v>
       </c>
       <c r="N94">
-        <v>-4.981479328000001</v>
+        <v>-5.063886712</v>
       </c>
       <c r="O94">
-        <v>-1.19555503872</v>
+        <v>-1.21533281088</v>
       </c>
       <c r="P94">
-        <v>-3.78592428928</v>
+        <v>-3.84855390112</v>
       </c>
       <c r="Q94">
-        <v>-3.445924289280001</v>
+        <v>-3.50855390112</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7430009846626954</v>
+        <v>0.8426011253287948</v>
       </c>
       <c r="T94">
-        <v>11.75581021541335</v>
+        <v>13.43521167475812</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08230583676399887</v>
+        <v>0.08142082776653653</v>
       </c>
       <c r="W94">
-        <v>0.2163922836910491</v>
+        <v>0.2166009688126507</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.342940986516662</v>
+        <v>0.3392534490272356</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2604209797687808</v>
+        <v>0.2623209797687808</v>
       </c>
       <c r="C95">
-        <v>-17.74300059822811</v>
+        <v>-18.16956696942279</v>
       </c>
       <c r="D95">
-        <v>9.19863940177189</v>
+        <v>9.121553030577211</v>
       </c>
       <c r="E95">
-        <v>31.65364</v>
+        <v>32.00312</v>
       </c>
       <c r="F95">
-        <v>32.50164</v>
+        <v>32.85112</v>
       </c>
       <c r="G95">
         <v>5.56</v>
@@ -9065,37 +9065,37 @@
         <v>2.6</v>
       </c>
       <c r="M95">
-        <v>7.663886712000001</v>
+        <v>7.746294096000001</v>
       </c>
       <c r="N95">
-        <v>-5.063886712</v>
+        <v>-5.146294096</v>
       </c>
       <c r="O95">
-        <v>-1.21533281088</v>
+        <v>-1.23511058304</v>
       </c>
       <c r="P95">
-        <v>-3.84855390112</v>
+        <v>-3.91118351296</v>
       </c>
       <c r="Q95">
-        <v>-3.50855390112</v>
+        <v>-3.57118351296</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8426011253287948</v>
+        <v>0.9754013128835942</v>
       </c>
       <c r="T95">
-        <v>13.43521167475812</v>
+        <v>15.67441362055114</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08142082776653653</v>
+        <v>0.0805546487477436</v>
       </c>
       <c r="W95">
-        <v>0.2166009688126507</v>
+        <v>0.2168052138252821</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3392534490272356</v>
+        <v>0.335644369782265</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2623209797687808</v>
+        <v>0.2642209797687807</v>
       </c>
       <c r="C96">
-        <v>-18.16956696942279</v>
+        <v>-18.59485208052648</v>
       </c>
       <c r="D96">
-        <v>9.121553030577211</v>
+        <v>9.045747919473527</v>
       </c>
       <c r="E96">
-        <v>32.00312</v>
+        <v>32.3526</v>
       </c>
       <c r="F96">
-        <v>32.85112</v>
+        <v>33.2006</v>
       </c>
       <c r="G96">
         <v>5.56</v>
@@ -9147,37 +9147,37 @@
         <v>2.6</v>
       </c>
       <c r="M96">
-        <v>7.746294096000001</v>
+        <v>7.82870148</v>
       </c>
       <c r="N96">
-        <v>-5.146294096</v>
+        <v>-5.22870148</v>
       </c>
       <c r="O96">
-        <v>-1.23511058304</v>
+        <v>-1.2548883552</v>
       </c>
       <c r="P96">
-        <v>-3.91118351296</v>
+        <v>-3.9738131248</v>
       </c>
       <c r="Q96">
-        <v>-3.57118351296</v>
+        <v>-3.6338131248</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9754013128835942</v>
+        <v>1.161321575460314</v>
       </c>
       <c r="T96">
-        <v>15.67441362055114</v>
+        <v>18.80929634466138</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0805546487477436</v>
+        <v>0.07970670507671471</v>
       </c>
       <c r="W96">
-        <v>0.2168052138252821</v>
+        <v>0.2170051589429107</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.335644369782265</v>
+        <v>0.332111271152978</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2642209797687807</v>
+        <v>0.2661209797687807</v>
       </c>
       <c r="C97">
-        <v>-18.59485208052648</v>
+        <v>-19.01888761217899</v>
       </c>
       <c r="D97">
-        <v>9.045747919473527</v>
+        <v>8.971192387821011</v>
       </c>
       <c r="E97">
-        <v>32.3526</v>
+        <v>32.70208</v>
       </c>
       <c r="F97">
-        <v>33.2006</v>
+        <v>33.55008</v>
       </c>
       <c r="G97">
         <v>5.56</v>
@@ -9229,37 +9229,37 @@
         <v>2.6</v>
       </c>
       <c r="M97">
-        <v>7.82870148</v>
+        <v>7.911108864000001</v>
       </c>
       <c r="N97">
-        <v>-5.22870148</v>
+        <v>-5.311108864000001</v>
       </c>
       <c r="O97">
-        <v>-1.2548883552</v>
+        <v>-1.27466612736</v>
       </c>
       <c r="P97">
-        <v>-3.9738131248</v>
+        <v>-4.036442736640002</v>
       </c>
       <c r="Q97">
-        <v>-3.6338131248</v>
+        <v>-3.696442736640002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.161321575460314</v>
+        <v>1.440201969325393</v>
       </c>
       <c r="T97">
-        <v>18.80929634466138</v>
+        <v>23.51162043082673</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07970670507671471</v>
+        <v>0.07887642689883226</v>
       </c>
       <c r="W97">
-        <v>0.2170051589429107</v>
+        <v>0.2172009385372554</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.332111271152978</v>
+        <v>0.3286517787451344</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2661209797687807</v>
+        <v>0.2680209797687808</v>
       </c>
       <c r="C98">
-        <v>-19.01888761217899</v>
+        <v>-19.44170420910422</v>
       </c>
       <c r="D98">
-        <v>8.971192387821011</v>
+        <v>8.897855790895781</v>
       </c>
       <c r="E98">
-        <v>32.70208</v>
+        <v>33.05156</v>
       </c>
       <c r="F98">
-        <v>33.55008</v>
+        <v>33.89956</v>
       </c>
       <c r="G98">
         <v>5.56</v>
@@ -9311,37 +9311,37 @@
         <v>2.6</v>
       </c>
       <c r="M98">
-        <v>7.911108864000001</v>
+        <v>7.993516248000001</v>
       </c>
       <c r="N98">
-        <v>-5.311108864000001</v>
+        <v>-5.393516248000001</v>
       </c>
       <c r="O98">
-        <v>-1.27466612736</v>
+        <v>-1.29444389952</v>
       </c>
       <c r="P98">
-        <v>-4.036442736640002</v>
+        <v>-4.099072348480001</v>
       </c>
       <c r="Q98">
-        <v>-3.696442736640002</v>
+        <v>-3.759072348480001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.440201969325389</v>
+        <v>1.905002625767185</v>
       </c>
       <c r="T98">
-        <v>23.51162043082667</v>
+        <v>31.34882724110223</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07887642689883226</v>
+        <v>0.07806326785863812</v>
       </c>
       <c r="W98">
-        <v>0.2172009385372554</v>
+        <v>0.2173926814389331</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3286517787451344</v>
+        <v>0.3252636160776587</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2680209797687808</v>
+        <v>0.2699209797687807</v>
       </c>
       <c r="C99">
-        <v>-19.44170420910422</v>
+        <v>-19.86333152210816</v>
       </c>
       <c r="D99">
-        <v>8.897855790895781</v>
+        <v>8.825708477891839</v>
       </c>
       <c r="E99">
-        <v>33.05156</v>
+        <v>33.40104</v>
       </c>
       <c r="F99">
-        <v>33.89956</v>
+        <v>34.24904</v>
       </c>
       <c r="G99">
         <v>5.56</v>
@@ -9393,37 +9393,37 @@
         <v>2.6</v>
       </c>
       <c r="M99">
-        <v>7.993516248000001</v>
+        <v>8.075923632</v>
       </c>
       <c r="N99">
-        <v>-5.393516248000001</v>
+        <v>-5.475923632000001</v>
       </c>
       <c r="O99">
-        <v>-1.29444389952</v>
+        <v>-1.31422167168</v>
       </c>
       <c r="P99">
-        <v>-4.099072348480001</v>
+        <v>-4.16170196032</v>
       </c>
       <c r="Q99">
-        <v>-3.759072348480001</v>
+        <v>-3.82170196032</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.905002625767185</v>
+        <v>2.834603938650777</v>
       </c>
       <c r="T99">
-        <v>31.34882724110223</v>
+        <v>47.02324086165333</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07806326785863812</v>
+        <v>0.07726670390089692</v>
       </c>
       <c r="W99">
-        <v>0.2173926814389331</v>
+        <v>0.2175805112201685</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3252636160776587</v>
+        <v>0.3219445995870704</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2699209797687807</v>
+        <v>0.2718209797687808</v>
       </c>
       <c r="C100">
-        <v>-19.86333152210816</v>
+        <v>-20.28379824805023</v>
       </c>
       <c r="D100">
-        <v>8.825708477891839</v>
+        <v>8.754721751949768</v>
       </c>
       <c r="E100">
-        <v>33.40104</v>
+        <v>33.75052</v>
       </c>
       <c r="F100">
-        <v>34.24904</v>
+        <v>34.59852</v>
       </c>
       <c r="G100">
         <v>5.56</v>
@@ -9475,37 +9475,37 @@
         <v>2.6</v>
       </c>
       <c r="M100">
-        <v>8.075923632</v>
+        <v>8.158331016</v>
       </c>
       <c r="N100">
-        <v>-5.475923632000001</v>
+        <v>-5.558331016</v>
       </c>
       <c r="O100">
-        <v>-1.31422167168</v>
+        <v>-1.33399944384</v>
       </c>
       <c r="P100">
-        <v>-4.16170196032</v>
+        <v>-4.224331572160001</v>
       </c>
       <c r="Q100">
-        <v>-3.82170196032</v>
+        <v>-3.884331572160001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.834603938650777</v>
+        <v>5.623407877301555</v>
       </c>
       <c r="T100">
-        <v>47.02324086165333</v>
+        <v>94.04648172330668</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07726670390089692</v>
+        <v>0.07648623214432219</v>
       </c>
       <c r="W100">
-        <v>0.2175805112201685</v>
+        <v>0.2177645464603689</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3219445995870704</v>
+        <v>0.3186926339346758</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2718209797687808</v>
-      </c>
-      <c r="C101">
-        <v>-20.28379824805023</v>
-      </c>
-      <c r="D101">
-        <v>8.754721751949768</v>
-      </c>
-      <c r="E101">
-        <v>33.75052</v>
-      </c>
-      <c r="F101">
-        <v>34.59852</v>
-      </c>
-      <c r="G101">
-        <v>5.56</v>
-      </c>
-      <c r="H101">
-        <v>34.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.94</v>
-      </c>
-      <c r="K101">
-        <v>0.34</v>
-      </c>
-      <c r="L101">
-        <v>2.6</v>
-      </c>
-      <c r="M101">
-        <v>8.158331016</v>
-      </c>
-      <c r="N101">
-        <v>-5.558331016</v>
-      </c>
-      <c r="O101">
-        <v>-1.33399944384</v>
-      </c>
-      <c r="P101">
-        <v>-4.224331572160001</v>
-      </c>
-      <c r="Q101">
-        <v>-3.884331572160001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.623407877301555</v>
-      </c>
-      <c r="T101">
-        <v>94.04648172330668</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07648623214432219</v>
-      </c>
-      <c r="W101">
-        <v>0.2177645464603689</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3186926339346758</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
